--- a/商户反馈近7天.xlsx
+++ b/商户反馈近7天.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E270"/>
+  <dimension ref="A1:E238"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -425,10 +425,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-17 18:12:25</v>
+        <v>2026-07-18 00:38:33</v>
       </c>
       <c r="B2" t="str">
-        <v>山东-济南-董其泽</v>
+        <v>江苏-南通-刘鑫</v>
       </c>
       <c r="C2" t="str">
         <v>质检</v>
@@ -442,10 +442,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-17 18:03:42</v>
+        <v>2026-07-17 23:42:07</v>
       </c>
       <c r="B3" t="str">
-        <v>云南-昆明-刘芳强</v>
+        <v>广东-深圳-苏宇晖</v>
       </c>
       <c r="C3" t="str">
         <v>质检</v>
@@ -459,10 +459,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-17 18:01:12</v>
+        <v>2026-07-17 22:34:57</v>
       </c>
       <c r="B4" t="str">
-        <v>云南-昆明-刘芳强</v>
+        <v>四川-成都-吕霞</v>
       </c>
       <c r="C4" t="str">
         <v>质检</v>
@@ -476,10 +476,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-17 17:48:13</v>
+        <v>2026-07-17 22:25:29</v>
       </c>
       <c r="B5" t="str">
-        <v>丁凤腾</v>
+        <v>重庆-徐若鸿</v>
       </c>
       <c r="C5" t="str">
         <v>质检</v>
@@ -493,10 +493,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-17 17:14:13</v>
+        <v>2026-07-17 21:42:15</v>
       </c>
       <c r="B6" t="str">
-        <v>浙江-金华-吴健鋆</v>
+        <v>李化学</v>
       </c>
       <c r="C6" t="str">
         <v>质检</v>
@@ -510,10 +510,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-17 17:02:36</v>
+        <v>2026-07-17 20:35:56</v>
       </c>
       <c r="B7" t="str">
-        <v>浙江-杭州-方来</v>
+        <v>江苏-南京-许国军</v>
       </c>
       <c r="C7" t="str">
         <v>质检</v>
@@ -527,10 +527,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-17 16:56:57</v>
+        <v>2026-07-17 20:28:57</v>
       </c>
       <c r="B8" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>天津张扬</v>
       </c>
       <c r="C8" t="str">
         <v>质检</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-17 16:39:25</v>
+        <v>2026-07-17 20:25:38</v>
       </c>
       <c r="B9" t="str">
-        <v>江西南昌聂宇杰</v>
+        <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C9" t="str">
         <v>质检</v>
@@ -556,15 +556,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E9" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-17 16:03:59</v>
+        <v>2026-07-17 19:12:32</v>
       </c>
       <c r="B10" t="str">
-        <v>安徽合肥王冬冬</v>
+        <v>江苏-南京-陈永祯</v>
       </c>
       <c r="C10" t="str">
         <v>质检</v>
@@ -573,15 +573,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E10" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-17 15:59:21</v>
+        <v>2026-07-17 19:05:26</v>
       </c>
       <c r="B11" t="str">
-        <v>广东佛山孟吉祥</v>
+        <v>江苏-南通-马志豪</v>
       </c>
       <c r="C11" t="str">
         <v>质检</v>
@@ -595,10 +595,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-17 15:13:47</v>
+        <v>2026-07-17 19:01:59</v>
       </c>
       <c r="B12" t="str">
-        <v>山东-济南-董其泽</v>
+        <v>江西-南昌-张小明</v>
       </c>
       <c r="C12" t="str">
         <v>质检</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-17 15:10:55</v>
+        <v>2026-07-17 18:58:33</v>
       </c>
       <c r="B13" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C13" t="str">
         <v>质检</v>
@@ -629,10 +629,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-17 15:10:44</v>
+        <v>2026-07-17 18:50:45</v>
       </c>
       <c r="B14" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>安徽-合肥-李怀志</v>
       </c>
       <c r="C14" t="str">
         <v>质检</v>
@@ -646,10 +646,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-17 15:10:14</v>
+        <v>2026-07-17 18:40:42</v>
       </c>
       <c r="B15" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>河南-郑州-黄倩</v>
       </c>
       <c r="C15" t="str">
         <v>质检</v>
@@ -658,15 +658,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E15" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-17 15:09:54</v>
+        <v>2026-07-17 18:12:25</v>
       </c>
       <c r="B16" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>山东-济南-董其泽</v>
       </c>
       <c r="C16" t="str">
         <v>质检</v>
@@ -675,15 +675,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E16" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-17 15:09:30</v>
+        <v>2026-07-17 18:03:42</v>
       </c>
       <c r="B17" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>云南-昆明-刘芳强</v>
       </c>
       <c r="C17" t="str">
         <v>质检</v>
@@ -697,10 +697,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-17 15:07:18</v>
+        <v>2026-07-17 18:01:12</v>
       </c>
       <c r="B18" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>云南-昆明-刘芳强</v>
       </c>
       <c r="C18" t="str">
         <v>质检</v>
@@ -714,10 +714,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-17 15:06:50</v>
+        <v>2026-07-17 17:48:13</v>
       </c>
       <c r="B19" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>丁凤腾</v>
       </c>
       <c r="C19" t="str">
         <v>质检</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-17 15:06:15</v>
+        <v>2026-07-17 17:14:13</v>
       </c>
       <c r="B20" t="str">
-        <v>山东-济南-董其泽</v>
+        <v>浙江-金华-吴健鋆</v>
       </c>
       <c r="C20" t="str">
         <v>质检</v>
@@ -748,10 +748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-17 14:40:16</v>
+        <v>2026-07-17 17:02:36</v>
       </c>
       <c r="B21" t="str">
-        <v>山东-济南-薛亚伟</v>
+        <v>浙江-杭州-方来</v>
       </c>
       <c r="C21" t="str">
         <v>质检</v>
@@ -765,10 +765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-17 14:27:31</v>
+        <v>2026-07-17 16:56:57</v>
       </c>
       <c r="B22" t="str">
-        <v>湖北-武汉-李俊杰</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C22" t="str">
         <v>质检</v>
@@ -777,15 +777,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E22" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-17 14:02:26</v>
+        <v>2026-07-17 16:39:25</v>
       </c>
       <c r="B23" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江西南昌聂宇杰</v>
       </c>
       <c r="C23" t="str">
         <v>质检</v>
@@ -794,15 +794,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E23" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-07-17 12:56:51</v>
+        <v>2026-07-17 16:03:59</v>
       </c>
       <c r="B24" t="str">
-        <v>辽宁-大连-郭浩</v>
+        <v>安徽合肥王冬冬</v>
       </c>
       <c r="C24" t="str">
         <v>质检</v>
@@ -811,15 +811,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E24" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-07-17 12:17:44</v>
+        <v>2026-07-17 15:59:21</v>
       </c>
       <c r="B25" t="str">
-        <v>江苏-南京-冯卯</v>
+        <v>广东佛山孟吉祥</v>
       </c>
       <c r="C25" t="str">
         <v>质检</v>
@@ -828,15 +828,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E25" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-07-17 11:23:16</v>
+        <v>2026-07-17 15:13:47</v>
       </c>
       <c r="B26" t="str">
-        <v>安徽-合肥-陈旭</v>
+        <v>山东-济南-董其泽</v>
       </c>
       <c r="C26" t="str">
         <v>质检</v>
@@ -850,10 +850,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-07-17 10:19:38</v>
+        <v>2026-07-17 15:10:55</v>
       </c>
       <c r="B27" t="str">
-        <v>吉林-长春-王彦文</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C27" t="str">
         <v>质检</v>
@@ -862,15 +862,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E27" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-07-17 09:54:49</v>
+        <v>2026-07-17 15:10:44</v>
       </c>
       <c r="B28" t="str">
-        <v>江苏-南京-冯卯</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C28" t="str">
         <v>质检</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-07-17 09:18:03</v>
+        <v>2026-07-17 15:10:14</v>
       </c>
       <c r="B29" t="str">
-        <v>黑龙江-哈尔滨-李士静</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C29" t="str">
         <v>质检</v>
@@ -896,15 +896,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E29" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-07-17 08:00:16</v>
+        <v>2026-07-17 15:09:54</v>
       </c>
       <c r="B30" t="str">
-        <v>辽宁-沈阳-姜闯</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C30" t="str">
         <v>质检</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-07-17 02:49:57</v>
+        <v>2026-07-17 15:09:30</v>
       </c>
       <c r="B31" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C31" t="str">
         <v>质检</v>
@@ -935,10 +935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-07-16 21:39:22</v>
+        <v>2026-07-17 15:07:18</v>
       </c>
       <c r="B32" t="str">
-        <v>江西-南昌-张小明</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C32" t="str">
         <v>质检</v>
@@ -952,10 +952,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-07-16 21:30:38</v>
+        <v>2026-07-17 15:06:50</v>
       </c>
       <c r="B33" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C33" t="str">
         <v>质检</v>
@@ -969,10 +969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-07-16 21:29:03</v>
+        <v>2026-07-17 15:06:15</v>
       </c>
       <c r="B34" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>山东-济南-董其泽</v>
       </c>
       <c r="C34" t="str">
         <v>质检</v>
@@ -981,15 +981,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E34" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-07-16 21:28:46</v>
+        <v>2026-07-17 14:40:16</v>
       </c>
       <c r="B35" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>山东-济南-薛亚伟</v>
       </c>
       <c r="C35" t="str">
         <v>质检</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-07-16 21:28:22</v>
+        <v>2026-07-17 14:27:31</v>
       </c>
       <c r="B36" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>湖北-武汉-李俊杰</v>
       </c>
       <c r="C36" t="str">
         <v>质检</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-07-16 20:52:32</v>
+        <v>2026-07-17 14:02:26</v>
       </c>
       <c r="B37" t="str">
         <v>广东-深圳-侯晓鹏</v>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-07-16 20:02:55</v>
+        <v>2026-07-17 12:56:51</v>
       </c>
       <c r="B38" t="str">
-        <v>云南-玉溪-吴正伟</v>
+        <v>辽宁-大连-郭浩</v>
       </c>
       <c r="C38" t="str">
         <v>质检</v>
@@ -1049,15 +1049,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E38" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-07-16 19:39:17</v>
+        <v>2026-07-17 12:17:44</v>
       </c>
       <c r="B39" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江苏-南京-冯卯</v>
       </c>
       <c r="C39" t="str">
         <v>质检</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-07-16 19:38:57</v>
+        <v>2026-07-17 11:23:16</v>
       </c>
       <c r="B40" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>安徽-合肥-陈旭</v>
       </c>
       <c r="C40" t="str">
         <v>质检</v>
@@ -1083,15 +1083,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E40" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-07-16 19:38:38</v>
+        <v>2026-07-17 10:19:38</v>
       </c>
       <c r="B41" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>吉林-长春-王彦文</v>
       </c>
       <c r="C41" t="str">
         <v>质检</v>
@@ -1100,15 +1100,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E41" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-07-16 19:29:10</v>
+        <v>2026-07-17 09:54:49</v>
       </c>
       <c r="B42" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江苏-南京-冯卯</v>
       </c>
       <c r="C42" t="str">
         <v>质检</v>
@@ -1117,15 +1117,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E42" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-07-16 19:04:50</v>
+        <v>2026-07-17 09:18:03</v>
       </c>
       <c r="B43" t="str">
-        <v>广东佛山孟吉祥</v>
+        <v>黑龙江-哈尔滨-李士静</v>
       </c>
       <c r="C43" t="str">
         <v>质检</v>
@@ -1134,15 +1134,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E43" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-07-16 17:42:48</v>
+        <v>2026-07-17 08:00:16</v>
       </c>
       <c r="B44" t="str">
-        <v>江西-南昌-涂荣志</v>
+        <v>辽宁-沈阳-姜闯</v>
       </c>
       <c r="C44" t="str">
         <v>质检</v>
@@ -1151,15 +1151,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E44" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-07-16 17:37:02</v>
+        <v>2026-07-17 02:49:57</v>
       </c>
       <c r="B45" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C45" t="str">
         <v>质检</v>
@@ -1168,15 +1168,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E45" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-07-16 17:28:52</v>
+        <v>2026-07-16 21:39:22</v>
       </c>
       <c r="B46" t="str">
-        <v>浙江-金华-吴健鋆</v>
+        <v>江西-南昌-张小明</v>
       </c>
       <c r="C46" t="str">
         <v>质检</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-07-16 17:13:02</v>
+        <v>2026-07-16 21:30:38</v>
       </c>
       <c r="B47" t="str">
-        <v>江苏-南京-冯卯</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C47" t="str">
         <v>质检</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-07-16 16:48:31</v>
+        <v>2026-07-16 21:29:03</v>
       </c>
       <c r="B48" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C48" t="str">
         <v>质检</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-07-16 16:47:25</v>
+        <v>2026-07-16 21:28:46</v>
       </c>
       <c r="B49" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C49" t="str">
         <v>质检</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-07-16 16:32:18</v>
+        <v>2026-07-16 21:28:22</v>
       </c>
       <c r="B50" t="str">
-        <v>河南-安阳-徐晓</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C50" t="str">
         <v>质检</v>
@@ -1253,12 +1253,12 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E50" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-07-16 14:36:03</v>
+        <v>2026-07-16 20:52:32</v>
       </c>
       <c r="B51" t="str">
         <v>广东-深圳-侯晓鹏</v>
@@ -1270,15 +1270,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E51" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-07-16 14:35:01</v>
+        <v>2026-07-16 20:02:55</v>
       </c>
       <c r="B52" t="str">
-        <v>福建-福州-林明铿</v>
+        <v>云南-玉溪-吴正伟</v>
       </c>
       <c r="C52" t="str">
         <v>质检</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-07-16 14:30:51</v>
+        <v>2026-07-16 19:39:17</v>
       </c>
       <c r="B53" t="str">
-        <v>福建三明魏女</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C53" t="str">
         <v>质检</v>
@@ -1304,15 +1304,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E53" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-07-16 14:22:14</v>
+        <v>2026-07-16 19:38:57</v>
       </c>
       <c r="B54" t="str">
-        <v>山东-济南-董其泽</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C54" t="str">
         <v>质检</v>
@@ -1321,15 +1321,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E54" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-07-16 14:00:58</v>
+        <v>2026-07-16 19:38:38</v>
       </c>
       <c r="B55" t="str">
-        <v>山东-菏泽-赵豪</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C55" t="str">
         <v>质检</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-07-16 13:35:04</v>
+        <v>2026-07-16 19:29:10</v>
       </c>
       <c r="B56" t="str">
-        <v>浙江-杭州-杨广恩</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C56" t="str">
         <v>质检</v>
@@ -1355,15 +1355,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E56" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-07-16 13:27:17</v>
+        <v>2026-07-16 19:04:50</v>
       </c>
       <c r="B57" t="str">
-        <v>重庆-重庆-辜宏亮</v>
+        <v>广东佛山孟吉祥</v>
       </c>
       <c r="C57" t="str">
         <v>质检</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-07-16 10:38:52</v>
+        <v>2026-07-16 17:42:48</v>
       </c>
       <c r="B58" t="str">
-        <v>山东-济南-薛亚伟</v>
+        <v>江西-南昌-涂荣志</v>
       </c>
       <c r="C58" t="str">
         <v>质检</v>
@@ -1389,15 +1389,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E58" t="str">
-        <v>处理中</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-07-16 10:04:58</v>
+        <v>2026-07-16 17:37:02</v>
       </c>
       <c r="B59" t="str">
-        <v>江苏-南通-刘鑫</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C59" t="str">
         <v>质检</v>
@@ -1406,15 +1406,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E59" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-07-16 09:58:14</v>
+        <v>2026-07-16 17:28:52</v>
       </c>
       <c r="B60" t="str">
-        <v>山西-太原-郑连珍</v>
+        <v>浙江-金华-吴健鋆</v>
       </c>
       <c r="C60" t="str">
         <v>质检</v>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-07-16 00:26:58</v>
+        <v>2026-07-16 17:13:02</v>
       </c>
       <c r="B61" t="str">
-        <v>江苏-淮安-夏前奇</v>
+        <v>江苏-南京-冯卯</v>
       </c>
       <c r="C61" t="str">
         <v>质检</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-07-15 23:10:46</v>
+        <v>2026-07-16 16:48:31</v>
       </c>
       <c r="B62" t="str">
-        <v>江西-南昌-王诚</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C62" t="str">
         <v>质检</v>
@@ -1462,10 +1462,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-07-15 22:47:10</v>
+        <v>2026-07-16 16:47:25</v>
       </c>
       <c r="B63" t="str">
-        <v>广东-广州-赵华武</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C63" t="str">
         <v>质检</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-07-15 21:58:48</v>
+        <v>2026-07-16 16:32:18</v>
       </c>
       <c r="B64" t="str">
-        <v>辽宁-沈阳-李雪婷</v>
+        <v>河南-安阳-徐晓</v>
       </c>
       <c r="C64" t="str">
         <v>质检</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-07-15 21:51:56</v>
+        <v>2026-07-16 14:36:03</v>
       </c>
       <c r="B65" t="str">
-        <v>江西-南昌-周凯</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C65" t="str">
         <v>质检</v>
@@ -1508,15 +1508,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E65" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-07-15 21:22:01</v>
+        <v>2026-07-16 14:35:01</v>
       </c>
       <c r="B66" t="str">
-        <v>李化学</v>
+        <v>福建-福州-林明铿</v>
       </c>
       <c r="C66" t="str">
         <v>质检</v>
@@ -1525,15 +1525,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E66" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-07-15 21:16:15</v>
+        <v>2026-07-16 14:30:51</v>
       </c>
       <c r="B67" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>福建三明魏女</v>
       </c>
       <c r="C67" t="str">
         <v>质检</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-07-15 21:05:20</v>
+        <v>2026-07-16 14:22:14</v>
       </c>
       <c r="B68" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>山东-济南-董其泽</v>
       </c>
       <c r="C68" t="str">
         <v>质检</v>
@@ -1559,15 +1559,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E68" t="str">
-        <v>处理中</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-07-15 20:58:21</v>
+        <v>2026-07-16 14:00:58</v>
       </c>
       <c r="B69" t="str">
-        <v>浙江-杭州-涂婷婷</v>
+        <v>山东-菏泽-赵豪</v>
       </c>
       <c r="C69" t="str">
         <v>质检</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-07-15 20:53:45</v>
+        <v>2026-07-16 13:35:04</v>
       </c>
       <c r="B70" t="str">
-        <v>江西-南昌-袁志</v>
+        <v>浙江-杭州-杨广恩</v>
       </c>
       <c r="C70" t="str">
         <v>质检</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-07-15 20:15:52</v>
+        <v>2026-07-16 13:27:17</v>
       </c>
       <c r="B71" t="str">
-        <v>江苏-常州-陈涛</v>
+        <v>重庆-重庆-辜宏亮</v>
       </c>
       <c r="C71" t="str">
         <v>质检</v>
@@ -1610,15 +1610,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E71" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-07-15 20:05:13</v>
+        <v>2026-07-16 10:38:52</v>
       </c>
       <c r="B72" t="str">
-        <v>李化学</v>
+        <v>山东-济南-薛亚伟</v>
       </c>
       <c r="C72" t="str">
         <v>质检</v>
@@ -1627,15 +1627,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E72" t="str">
-        <v>已处理</v>
+        <v>处理中</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-07-15 19:58:35</v>
+        <v>2026-07-16 10:04:58</v>
       </c>
       <c r="B73" t="str">
-        <v>浙江-绍兴-张磊</v>
+        <v>江苏-南通-刘鑫</v>
       </c>
       <c r="C73" t="str">
         <v>质检</v>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-07-15 19:53:56</v>
+        <v>2026-07-16 09:58:14</v>
       </c>
       <c r="B74" t="str">
-        <v>山东-济宁-于鲁川</v>
+        <v>山西-太原-郑连珍</v>
       </c>
       <c r="C74" t="str">
         <v>质检</v>
@@ -1661,15 +1661,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E74" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-07-15 19:38:21</v>
+        <v>2026-07-16 00:26:58</v>
       </c>
       <c r="B75" t="str">
-        <v>江苏-常州-陈涛</v>
+        <v>江苏-淮安-夏前奇</v>
       </c>
       <c r="C75" t="str">
         <v>质检</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-07-15 19:37:55</v>
+        <v>2026-07-15 23:10:46</v>
       </c>
       <c r="B76" t="str">
-        <v>江苏-常州-陈涛</v>
+        <v>江西-南昌-王诚</v>
       </c>
       <c r="C76" t="str">
         <v>质检</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-07-15 18:12:11</v>
+        <v>2026-07-15 22:47:10</v>
       </c>
       <c r="B77" t="str">
-        <v>丁凤腾</v>
+        <v>广东-广州-赵华武</v>
       </c>
       <c r="C77" t="str">
         <v>质检</v>
@@ -1712,15 +1712,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E77" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-07-15 17:13:28</v>
+        <v>2026-07-15 21:58:48</v>
       </c>
       <c r="B78" t="str">
-        <v>浙江-杭州-王华山</v>
+        <v>辽宁-沈阳-李雪婷</v>
       </c>
       <c r="C78" t="str">
         <v>质检</v>
@@ -1729,15 +1729,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E78" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-07-15 16:19:49</v>
+        <v>2026-07-15 21:51:56</v>
       </c>
       <c r="B79" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>江西-南昌-周凯</v>
       </c>
       <c r="C79" t="str">
         <v>质检</v>
@@ -1746,15 +1746,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E79" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-07-15 16:01:12</v>
+        <v>2026-07-15 21:22:01</v>
       </c>
       <c r="B80" t="str">
-        <v>广东-深圳-任迎超</v>
+        <v>李化学</v>
       </c>
       <c r="C80" t="str">
         <v>质检</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-07-15 15:27:07</v>
+        <v>2026-07-15 21:16:15</v>
       </c>
       <c r="B81" t="str">
-        <v>甘肃-天水-王娟</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C81" t="str">
         <v>质检</v>
@@ -1780,15 +1780,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E81" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-07-15 14:53:29</v>
+        <v>2026-07-15 21:05:20</v>
       </c>
       <c r="B82" t="str">
-        <v>山东-济南-房超</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C82" t="str">
         <v>质检</v>
@@ -1797,15 +1797,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E82" t="str">
-        <v>已处理</v>
+        <v>处理中</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-07-15 14:48:27</v>
+        <v>2026-07-15 20:58:21</v>
       </c>
       <c r="B83" t="str">
-        <v>山东-济南-房超</v>
+        <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C83" t="str">
         <v>质检</v>
@@ -1814,15 +1814,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E83" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-07-15 14:34:28</v>
+        <v>2026-07-15 20:53:45</v>
       </c>
       <c r="B84" t="str">
-        <v>河北-邢台-付春静</v>
+        <v>江西-南昌-袁志</v>
       </c>
       <c r="C84" t="str">
         <v>质检</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026-07-15 14:06:49</v>
+        <v>2026-07-15 20:15:52</v>
       </c>
       <c r="B85" t="str">
-        <v>浙江-杭州-郑培煌</v>
+        <v>江苏-常州-陈涛</v>
       </c>
       <c r="C85" t="str">
         <v>质检</v>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026-07-15 13:15:46</v>
+        <v>2026-07-15 20:05:13</v>
       </c>
       <c r="B86" t="str">
-        <v>广东佛山孟吉祥</v>
+        <v>李化学</v>
       </c>
       <c r="C86" t="str">
         <v>质检</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2026-07-15 12:51:24</v>
+        <v>2026-07-15 19:58:35</v>
       </c>
       <c r="B87" t="str">
-        <v>江苏-南京-冯卯</v>
+        <v>浙江-绍兴-张磊</v>
       </c>
       <c r="C87" t="str">
         <v>质检</v>
@@ -1882,15 +1882,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E87" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026-07-15 12:05:52</v>
+        <v>2026-07-15 19:53:56</v>
       </c>
       <c r="B88" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>山东-济宁-于鲁川</v>
       </c>
       <c r="C88" t="str">
         <v>质检</v>
@@ -1899,15 +1899,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E88" t="str">
-        <v>处理中</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2026-07-15 11:48:41</v>
+        <v>2026-07-15 19:38:21</v>
       </c>
       <c r="B89" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>江苏-常州-陈涛</v>
       </c>
       <c r="C89" t="str">
         <v>质检</v>
@@ -1916,15 +1916,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E89" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2026-07-15 11:39:58</v>
+        <v>2026-07-15 19:37:55</v>
       </c>
       <c r="B90" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>江苏-常州-陈涛</v>
       </c>
       <c r="C90" t="str">
         <v>质检</v>
@@ -1933,15 +1933,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E90" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2026-07-15 11:22:48</v>
+        <v>2026-07-15 18:12:11</v>
       </c>
       <c r="B91" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>丁凤腾</v>
       </c>
       <c r="C91" t="str">
         <v>质检</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2026-07-15 11:18:59</v>
+        <v>2026-07-15 17:13:28</v>
       </c>
       <c r="B92" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>浙江-杭州-王华山</v>
       </c>
       <c r="C92" t="str">
         <v>质检</v>
@@ -1967,15 +1967,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E92" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2026-07-15 11:17:25</v>
+        <v>2026-07-15 16:19:49</v>
       </c>
       <c r="B93" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C93" t="str">
         <v>质检</v>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2026-07-15 10:36:29</v>
+        <v>2026-07-15 16:01:12</v>
       </c>
       <c r="B94" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>广东-深圳-任迎超</v>
       </c>
       <c r="C94" t="str">
         <v>质检</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2026-07-15 10:25:18</v>
+        <v>2026-07-15 15:27:07</v>
       </c>
       <c r="B95" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>甘肃-天水-王娟</v>
       </c>
       <c r="C95" t="str">
         <v>质检</v>
@@ -2018,15 +2018,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E95" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2026-07-15 10:07:26</v>
+        <v>2026-07-15 14:53:29</v>
       </c>
       <c r="B96" t="str">
-        <v>河南-郑州-黄倩</v>
+        <v>山东-济南-房超</v>
       </c>
       <c r="C96" t="str">
         <v>质检</v>
@@ -2035,15 +2035,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E96" t="str">
-        <v>处理中</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2026-07-15 08:59:57</v>
+        <v>2026-07-15 14:48:27</v>
       </c>
       <c r="B97" t="str">
-        <v>云南-昆明-米丹</v>
+        <v>山东-济南-房超</v>
       </c>
       <c r="C97" t="str">
         <v>质检</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2026-07-15 08:22:21</v>
+        <v>2026-07-15 14:34:28</v>
       </c>
       <c r="B98" t="str">
-        <v>安徽合肥王冬冬</v>
+        <v>河北-邢台-付春静</v>
       </c>
       <c r="C98" t="str">
         <v>质检</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2026-07-15 08:20:51</v>
+        <v>2026-07-15 14:06:49</v>
       </c>
       <c r="B99" t="str">
-        <v>安徽合肥王冬冬</v>
+        <v>浙江-杭州-郑培煌</v>
       </c>
       <c r="C99" t="str">
         <v>质检</v>
@@ -2086,15 +2086,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E99" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2026-07-15 08:20:35</v>
+        <v>2026-07-15 13:15:46</v>
       </c>
       <c r="B100" t="str">
-        <v>李化学</v>
+        <v>广东佛山孟吉祥</v>
       </c>
       <c r="C100" t="str">
         <v>质检</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2026-07-15 01:35:31</v>
+        <v>2026-07-15 12:51:24</v>
       </c>
       <c r="B101" t="str">
-        <v>广东-深圳-苏宇晖</v>
+        <v>江苏-南京-冯卯</v>
       </c>
       <c r="C101" t="str">
         <v>质检</v>
@@ -2120,15 +2120,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E101" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2026-07-14 22:50:39</v>
+        <v>2026-07-15 12:05:52</v>
       </c>
       <c r="B102" t="str">
-        <v>江苏-南通-刘鑫</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C102" t="str">
         <v>质检</v>
@@ -2137,15 +2137,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E102" t="str">
-        <v>已处理</v>
+        <v>处理中</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2026-07-14 22:47:39</v>
+        <v>2026-07-15 11:48:41</v>
       </c>
       <c r="B103" t="str">
-        <v>江苏-南通-刘鑫</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C103" t="str">
         <v>质检</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2026-07-14 22:24:27</v>
+        <v>2026-07-15 11:39:58</v>
       </c>
       <c r="B104" t="str">
-        <v>江苏-淮安-张弛</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C104" t="str">
         <v>质检</v>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2026-07-14 21:20:34</v>
+        <v>2026-07-15 11:22:48</v>
       </c>
       <c r="B105" t="str">
-        <v>江苏-淮安-张弛</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C105" t="str">
         <v>质检</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2026-07-14 21:20:06</v>
+        <v>2026-07-15 11:18:59</v>
       </c>
       <c r="B106" t="str">
-        <v>江苏-淮安-张弛</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C106" t="str">
         <v>质检</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2026-07-14 21:19:52</v>
+        <v>2026-07-15 11:17:25</v>
       </c>
       <c r="B107" t="str">
-        <v>江苏-淮安-张弛</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C107" t="str">
         <v>质检</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2026-07-14 21:07:20</v>
+        <v>2026-07-15 10:36:29</v>
       </c>
       <c r="B108" t="str">
-        <v>广东-佛山-刘海滢</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C108" t="str">
         <v>质检</v>
@@ -2239,15 +2239,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E108" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2026-07-14 19:26:41</v>
+        <v>2026-07-15 10:25:18</v>
       </c>
       <c r="B109" t="str">
-        <v>河南-郑州-黄倩</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C109" t="str">
         <v>质检</v>
@@ -2256,15 +2256,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E109" t="str">
-        <v>处理中</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2026-07-14 18:34:33</v>
+        <v>2026-07-15 10:07:26</v>
       </c>
       <c r="B110" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>河南-郑州-黄倩</v>
       </c>
       <c r="C110" t="str">
         <v>质检</v>
@@ -2273,15 +2273,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E110" t="str">
-        <v>已处理</v>
+        <v>处理中</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2026-07-14 18:33:26</v>
+        <v>2026-07-15 08:59:57</v>
       </c>
       <c r="B111" t="str">
-        <v>广东佛山孟吉祥</v>
+        <v>云南-昆明-米丹</v>
       </c>
       <c r="C111" t="str">
         <v>质检</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2026-07-14 18:12:55</v>
+        <v>2026-07-15 08:22:21</v>
       </c>
       <c r="B112" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>安徽合肥王冬冬</v>
       </c>
       <c r="C112" t="str">
         <v>质检</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2026-07-14 18:11:00</v>
+        <v>2026-07-15 08:20:51</v>
       </c>
       <c r="B113" t="str">
-        <v>云南-昆明-郎雄伟</v>
+        <v>安徽合肥王冬冬</v>
       </c>
       <c r="C113" t="str">
         <v>质检</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2026-07-14 17:02:27</v>
+        <v>2026-07-15 08:20:35</v>
       </c>
       <c r="B114" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>李化学</v>
       </c>
       <c r="C114" t="str">
         <v>质检</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2026-07-14 15:50:53</v>
+        <v>2026-07-15 01:35:31</v>
       </c>
       <c r="B115" t="str">
-        <v>广东-揭阳-杜晓彬</v>
+        <v>广东-深圳-苏宇晖</v>
       </c>
       <c r="C115" t="str">
         <v>质检</v>
@@ -2358,15 +2358,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E115" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-07-14 15:33:36</v>
+        <v>2026-07-14 22:50:39</v>
       </c>
       <c r="B116" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>江苏-南通-刘鑫</v>
       </c>
       <c r="C116" t="str">
         <v>质检</v>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2026-07-14 15:27:16</v>
+        <v>2026-07-14 22:47:39</v>
       </c>
       <c r="B117" t="str">
-        <v>安徽-芜湖-包飞</v>
+        <v>江苏-南通-刘鑫</v>
       </c>
       <c r="C117" t="str">
         <v>质检</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-07-14 14:22:46</v>
+        <v>2026-07-14 22:24:27</v>
       </c>
       <c r="B118" t="str">
-        <v>湖南-长沙-罗明凯</v>
+        <v>江苏-淮安-张弛</v>
       </c>
       <c r="C118" t="str">
         <v>质检</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-07-14 14:02:42</v>
+        <v>2026-07-14 21:20:34</v>
       </c>
       <c r="B119" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江苏-淮安-张弛</v>
       </c>
       <c r="C119" t="str">
         <v>质检</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2026-07-14 14:00:45</v>
+        <v>2026-07-14 21:20:06</v>
       </c>
       <c r="B120" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>江苏-淮安-张弛</v>
       </c>
       <c r="C120" t="str">
         <v>质检</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2026-07-14 14:00:27</v>
+        <v>2026-07-14 21:19:52</v>
       </c>
       <c r="B121" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>江苏-淮安-张弛</v>
       </c>
       <c r="C121" t="str">
         <v>质检</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2026-07-14 13:59:42</v>
+        <v>2026-07-14 21:07:20</v>
       </c>
       <c r="B122" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>广东-佛山-刘海滢</v>
       </c>
       <c r="C122" t="str">
         <v>质检</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>2026-07-14 13:54:22</v>
+        <v>2026-07-14 19:26:41</v>
       </c>
       <c r="B123" t="str">
-        <v>江苏-无锡-刘雪伟</v>
+        <v>河南-郑州-黄倩</v>
       </c>
       <c r="C123" t="str">
         <v>质检</v>
@@ -2494,15 +2494,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E123" t="str">
-        <v>已评价</v>
+        <v>处理中</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2026-07-14 13:43:42</v>
+        <v>2026-07-14 18:34:33</v>
       </c>
       <c r="B124" t="str">
-        <v>湖北-武汉-李俊杰</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C124" t="str">
         <v>质检</v>
@@ -2511,15 +2511,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E124" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2026-07-14 13:39:29</v>
+        <v>2026-07-14 18:33:26</v>
       </c>
       <c r="B125" t="str">
-        <v>浙江-杭州-向东</v>
+        <v>广东佛山孟吉祥</v>
       </c>
       <c r="C125" t="str">
         <v>质检</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>2026-07-14 10:57:20</v>
+        <v>2026-07-14 18:12:55</v>
       </c>
       <c r="B126" t="str">
-        <v>山西-太原-郑连珍</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C126" t="str">
         <v>质检</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>2026-07-14 10:54:52</v>
+        <v>2026-07-14 18:11:00</v>
       </c>
       <c r="B127" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>云南-昆明-郎雄伟</v>
       </c>
       <c r="C127" t="str">
         <v>质检</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2026-07-14 10:51:15</v>
+        <v>2026-07-14 17:02:27</v>
       </c>
       <c r="B128" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C128" t="str">
         <v>质检</v>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2026-07-14 10:49:17</v>
+        <v>2026-07-14 15:50:53</v>
       </c>
       <c r="B129" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>广东-揭阳-杜晓彬</v>
       </c>
       <c r="C129" t="str">
         <v>质检</v>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2026-07-14 10:48:44</v>
+        <v>2026-07-14 15:33:36</v>
       </c>
       <c r="B130" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C130" t="str">
         <v>质检</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2026-07-14 10:41:01</v>
+        <v>2026-07-14 15:27:16</v>
       </c>
       <c r="B131" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>安徽-芜湖-包飞</v>
       </c>
       <c r="C131" t="str">
         <v>质检</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2026-07-14 10:37:29</v>
+        <v>2026-07-14 14:22:46</v>
       </c>
       <c r="B132" t="str">
-        <v>安徽-合肥-张荣营</v>
+        <v>湖南-长沙-罗明凯</v>
       </c>
       <c r="C132" t="str">
         <v>质检</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2026-07-14 10:34:21</v>
+        <v>2026-07-14 14:02:42</v>
       </c>
       <c r="B133" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C133" t="str">
         <v>质检</v>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2026-07-14 10:33:26</v>
+        <v>2026-07-14 14:00:45</v>
       </c>
       <c r="B134" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C134" t="str">
         <v>质检</v>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>2026-07-14 10:21:14</v>
+        <v>2026-07-14 14:00:27</v>
       </c>
       <c r="B135" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C135" t="str">
         <v>质检</v>
@@ -2703,10 +2703,10 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>2026-07-14 10:18:08</v>
+        <v>2026-07-14 13:59:42</v>
       </c>
       <c r="B136" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C136" t="str">
         <v>质检</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2026-07-14 10:07:37</v>
+        <v>2026-07-14 13:54:22</v>
       </c>
       <c r="B137" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>江苏-无锡-刘雪伟</v>
       </c>
       <c r="C137" t="str">
         <v>质检</v>
@@ -2732,15 +2732,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E137" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2026-07-14 10:06:47</v>
+        <v>2026-07-14 13:43:42</v>
       </c>
       <c r="B138" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>湖北-武汉-李俊杰</v>
       </c>
       <c r="C138" t="str">
         <v>质检</v>
@@ -2749,15 +2749,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E138" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>2026-07-14 09:36:24</v>
+        <v>2026-07-14 13:39:29</v>
       </c>
       <c r="B139" t="str">
-        <v>江苏-南京-冯卯</v>
+        <v>浙江-杭州-向东</v>
       </c>
       <c r="C139" t="str">
         <v>质检</v>
@@ -2771,10 +2771,10 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2026-07-13 21:40:28</v>
+        <v>2026-07-14 10:57:20</v>
       </c>
       <c r="B140" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>山西-太原-郑连珍</v>
       </c>
       <c r="C140" t="str">
         <v>质检</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>2026-07-13 21:06:46</v>
+        <v>2026-07-14 10:54:52</v>
       </c>
       <c r="B141" t="str">
-        <v>辽宁-沈阳-王文超</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C141" t="str">
         <v>质检</v>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2026-07-13 21:05:00</v>
+        <v>2026-07-14 10:51:15</v>
       </c>
       <c r="B142" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C142" t="str">
         <v>质检</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>2026-07-13 20:34:01</v>
+        <v>2026-07-14 10:49:17</v>
       </c>
       <c r="B143" t="str">
-        <v>安徽-合肥-韦波</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C143" t="str">
         <v>质检</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>2026-07-13 20:14:02</v>
+        <v>2026-07-14 10:48:44</v>
       </c>
       <c r="B144" t="str">
-        <v>重庆-徐若鸿</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C144" t="str">
         <v>质检</v>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>2026-07-13 20:06:44</v>
+        <v>2026-07-14 10:41:01</v>
       </c>
       <c r="B145" t="str">
-        <v>福建-南平-葛荣彪</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C145" t="str">
         <v>质检</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>2026-07-13 20:01:38</v>
+        <v>2026-07-14 10:37:29</v>
       </c>
       <c r="B146" t="str">
-        <v>辽宁-沈阳-王文超</v>
+        <v>安徽-合肥-张荣营</v>
       </c>
       <c r="C146" t="str">
         <v>质检</v>
@@ -2885,15 +2885,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E146" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>2026-07-13 19:50:45</v>
+        <v>2026-07-14 10:34:21</v>
       </c>
       <c r="B147" t="str">
-        <v>北京-北京-刘英琪</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C147" t="str">
         <v>质检</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>2026-07-13 19:31:43</v>
+        <v>2026-07-14 10:33:26</v>
       </c>
       <c r="B148" t="str">
-        <v>福建-南平-葛荣彪</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C148" t="str">
         <v>质检</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>2026-07-13 19:31:00</v>
+        <v>2026-07-14 10:21:14</v>
       </c>
       <c r="B149" t="str">
-        <v>福建-南平-葛荣彪</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C149" t="str">
         <v>质检</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>2026-07-13 19:30:35</v>
+        <v>2026-07-14 10:18:08</v>
       </c>
       <c r="B150" t="str">
-        <v>福建-南平-葛荣彪</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C150" t="str">
         <v>质检</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>2026-07-13 19:30:11</v>
+        <v>2026-07-14 10:07:37</v>
       </c>
       <c r="B151" t="str">
-        <v>福建-南平-葛荣彪</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C151" t="str">
         <v>质检</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>2026-07-13 19:04:31</v>
+        <v>2026-07-14 10:06:47</v>
       </c>
       <c r="B152" t="str">
-        <v>河北-邢台-付春静</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C152" t="str">
         <v>质检</v>
@@ -2987,15 +2987,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E152" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>2026-07-13 18:54:16</v>
+        <v>2026-07-14 09:36:24</v>
       </c>
       <c r="B153" t="str">
-        <v>河北-邢台-付春静</v>
+        <v>江苏-南京-冯卯</v>
       </c>
       <c r="C153" t="str">
         <v>质检</v>
@@ -3004,15 +3004,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E153" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>2026-07-13 18:12:10</v>
+        <v>2026-07-13 21:40:28</v>
       </c>
       <c r="B154" t="str">
-        <v>重庆-重庆-廖青山</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C154" t="str">
         <v>质检</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>2026-07-13 17:52:28</v>
+        <v>2026-07-13 21:06:46</v>
       </c>
       <c r="B155" t="str">
-        <v>甘肃-天水-牛田雨</v>
+        <v>辽宁-沈阳-王文超</v>
       </c>
       <c r="C155" t="str">
         <v>质检</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>2026-07-13 17:29:39</v>
+        <v>2026-07-13 21:05:00</v>
       </c>
       <c r="B156" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C156" t="str">
         <v>质检</v>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>2026-07-13 17:27:16</v>
+        <v>2026-07-13 20:34:01</v>
       </c>
       <c r="B157" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
+        <v>安徽-合肥-韦波</v>
       </c>
       <c r="C157" t="str">
         <v>质检</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>2026-07-13 17:26:02</v>
+        <v>2026-07-13 20:14:02</v>
       </c>
       <c r="B158" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
+        <v>重庆-徐若鸿</v>
       </c>
       <c r="C158" t="str">
         <v>质检</v>
@@ -3094,10 +3094,10 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>2026-07-13 17:20:44</v>
+        <v>2026-07-13 20:06:44</v>
       </c>
       <c r="B159" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
+        <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C159" t="str">
         <v>质检</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>2026-07-13 17:06:45</v>
+        <v>2026-07-13 20:01:38</v>
       </c>
       <c r="B160" t="str">
-        <v>福建-南平-葛荣彪</v>
+        <v>辽宁-沈阳-王文超</v>
       </c>
       <c r="C160" t="str">
         <v>质检</v>
@@ -3123,15 +3123,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E160" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>2026-07-13 17:06:30</v>
+        <v>2026-07-13 19:50:45</v>
       </c>
       <c r="B161" t="str">
-        <v>福建-南平-葛荣彪</v>
+        <v>北京-北京-刘英琪</v>
       </c>
       <c r="C161" t="str">
         <v>质检</v>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>2026-07-13 16:47:32</v>
+        <v>2026-07-13 19:31:43</v>
       </c>
       <c r="B162" t="str">
-        <v>广东-深圳-张洲豪</v>
+        <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C162" t="str">
         <v>质检</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>2026-07-13 15:46:10</v>
+        <v>2026-07-13 19:31:00</v>
       </c>
       <c r="B163" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C163" t="str">
         <v>质检</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>2026-07-13 15:09:44</v>
+        <v>2026-07-13 19:30:35</v>
       </c>
       <c r="B164" t="str">
-        <v>山东-济南-房超</v>
+        <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C164" t="str">
         <v>质检</v>
@@ -3196,10 +3196,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>2026-07-13 14:59:21</v>
+        <v>2026-07-13 19:30:11</v>
       </c>
       <c r="B165" t="str">
-        <v>四川-成都-王付强</v>
+        <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C165" t="str">
         <v>质检</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>2026-07-13 11:30:20</v>
+        <v>2026-07-13 19:04:31</v>
       </c>
       <c r="B166" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>河北-邢台-付春静</v>
       </c>
       <c r="C166" t="str">
         <v>质检</v>
@@ -3225,15 +3225,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E166" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>2026-07-13 11:16:38</v>
+        <v>2026-07-13 18:54:16</v>
       </c>
       <c r="B167" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>河北-邢台-付春静</v>
       </c>
       <c r="C167" t="str">
         <v>质检</v>
@@ -3242,15 +3242,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E167" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>2026-07-13 10:46:56</v>
+        <v>2026-07-13 18:12:10</v>
       </c>
       <c r="B168" t="str">
-        <v>河南-郑州-黄倩</v>
+        <v>重庆-重庆-廖青山</v>
       </c>
       <c r="C168" t="str">
         <v>质检</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>2026-07-13 09:22:33</v>
+        <v>2026-07-13 17:52:28</v>
       </c>
       <c r="B169" t="str">
-        <v>浙江-杭州-涂婷婷</v>
+        <v>甘肃-天水-牛田雨</v>
       </c>
       <c r="C169" t="str">
         <v>质检</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>2026-07-12 21:35:07</v>
+        <v>2026-07-13 17:29:39</v>
       </c>
       <c r="B170" t="str">
-        <v>江苏-南京-许国军</v>
+        <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C170" t="str">
         <v>质检</v>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>2026-07-12 21:08:03</v>
+        <v>2026-07-13 17:27:16</v>
       </c>
       <c r="B171" t="str">
-        <v>江苏-无锡-何炳爱</v>
+        <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C171" t="str">
         <v>质检</v>
@@ -3315,27 +3315,27 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>2026-07-12 18:56:21</v>
+        <v>2026-07-13 17:26:02</v>
       </c>
       <c r="B172" t="str">
-        <v>四川-成都-程安材</v>
+        <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C172" t="str">
-        <v>售后</v>
+        <v>质检</v>
       </c>
       <c r="D172" t="str">
-        <v>售后退回有机损</v>
+        <v>质检报告不认可</v>
       </c>
       <c r="E172" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>2026-07-12 18:51:37</v>
+        <v>2026-07-13 17:20:44</v>
       </c>
       <c r="B173" t="str">
-        <v>四川-成都-王付强</v>
+        <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C173" t="str">
         <v>质检</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>2026-07-12 18:51:06</v>
+        <v>2026-07-13 17:06:45</v>
       </c>
       <c r="B174" t="str">
-        <v>安徽-亳州-陆盼盼</v>
+        <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C174" t="str">
         <v>质检</v>
@@ -3366,10 +3366,10 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>2026-07-12 18:48:25</v>
+        <v>2026-07-13 17:06:30</v>
       </c>
       <c r="B175" t="str">
-        <v>安徽-亳州-陆盼盼</v>
+        <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C175" t="str">
         <v>质检</v>
@@ -3383,10 +3383,10 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>2026-07-12 18:46:15</v>
+        <v>2026-07-13 16:47:32</v>
       </c>
       <c r="B176" t="str">
-        <v>河南-郑州-季森森</v>
+        <v>广东-深圳-张洲豪</v>
       </c>
       <c r="C176" t="str">
         <v>质检</v>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>2026-07-12 18:45:35</v>
+        <v>2026-07-13 15:46:10</v>
       </c>
       <c r="B177" t="str">
-        <v>河南-郑州-季森森</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C177" t="str">
         <v>质检</v>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>2026-07-12 17:40:13</v>
+        <v>2026-07-13 15:09:44</v>
       </c>
       <c r="B178" t="str">
-        <v>福建-福州-王忠明</v>
+        <v>山东-济南-房超</v>
       </c>
       <c r="C178" t="str">
         <v>质检</v>
@@ -3429,15 +3429,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E178" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>2026-07-12 17:25:09</v>
+        <v>2026-07-13 14:59:21</v>
       </c>
       <c r="B179" t="str">
-        <v>辽宁-沈阳-王海青</v>
+        <v>四川-成都-王付强</v>
       </c>
       <c r="C179" t="str">
         <v>质检</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>2026-07-12 17:16:28</v>
+        <v>2026-07-13 11:30:20</v>
       </c>
       <c r="B180" t="str">
-        <v>江苏-苏州-黄迪孟</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C180" t="str">
         <v>质检</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>2026-07-12 16:45:02</v>
+        <v>2026-07-13 11:16:38</v>
       </c>
       <c r="B181" t="str">
-        <v>山东-济南-戴志鹏</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C181" t="str">
         <v>质检</v>
@@ -3485,10 +3485,10 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>2026-07-12 16:34:21</v>
+        <v>2026-07-13 10:46:56</v>
       </c>
       <c r="B182" t="str">
-        <v>湖北-武汉-黄武</v>
+        <v>河南-郑州-黄倩</v>
       </c>
       <c r="C182" t="str">
         <v>质检</v>
@@ -3497,15 +3497,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E182" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>2026-07-12 16:25:40</v>
+        <v>2026-07-13 09:22:33</v>
       </c>
       <c r="B183" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C183" t="str">
         <v>质检</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>2026-07-12 16:04:05</v>
+        <v>2026-07-12 21:35:07</v>
       </c>
       <c r="B184" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
+        <v>江苏-南京-许国军</v>
       </c>
       <c r="C184" t="str">
         <v>质检</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>2026-07-12 16:03:47</v>
+        <v>2026-07-12 21:08:03</v>
       </c>
       <c r="B185" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江苏-无锡-何炳爱</v>
       </c>
       <c r="C185" t="str">
         <v>质检</v>
@@ -3548,32 +3548,32 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E185" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>2026-07-12 15:15:47</v>
+        <v>2026-07-12 18:56:21</v>
       </c>
       <c r="B186" t="str">
-        <v>河南-郑州-焦威建</v>
+        <v>四川-成都-程安材</v>
       </c>
       <c r="C186" t="str">
-        <v>质检</v>
+        <v>售后</v>
       </c>
       <c r="D186" t="str">
-        <v>质检报告不认可</v>
+        <v>售后退回有机损</v>
       </c>
       <c r="E186" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>2026-07-12 14:40:24</v>
+        <v>2026-07-12 18:51:37</v>
       </c>
       <c r="B187" t="str">
-        <v>广东-深圳-陈敬丽</v>
+        <v>四川-成都-王付强</v>
       </c>
       <c r="C187" t="str">
         <v>质检</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>2026-07-12 14:31:08</v>
+        <v>2026-07-12 18:51:06</v>
       </c>
       <c r="B188" t="str">
-        <v>安徽-阜阳-赵子军</v>
+        <v>安徽-亳州-陆盼盼</v>
       </c>
       <c r="C188" t="str">
         <v>质检</v>
@@ -3599,15 +3599,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E188" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>2026-07-12 12:30:41</v>
+        <v>2026-07-12 18:48:25</v>
       </c>
       <c r="B189" t="str">
-        <v>广东-深圳-迟恭彦</v>
+        <v>安徽-亳州-陆盼盼</v>
       </c>
       <c r="C189" t="str">
         <v>质检</v>
@@ -3621,10 +3621,10 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>2026-07-12 12:16:48</v>
+        <v>2026-07-12 18:46:15</v>
       </c>
       <c r="B190" t="str">
-        <v>河北-石家庄-赵飞</v>
+        <v>河南-郑州-季森森</v>
       </c>
       <c r="C190" t="str">
         <v>质检</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>2026-07-12 10:32:13</v>
+        <v>2026-07-12 18:45:35</v>
       </c>
       <c r="B191" t="str">
-        <v>浙江-杭州-涂婷婷</v>
+        <v>河南-郑州-季森森</v>
       </c>
       <c r="C191" t="str">
         <v>质检</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>2026-07-12 10:22:55</v>
+        <v>2026-07-12 17:40:13</v>
       </c>
       <c r="B192" t="str">
-        <v>四川-成都-程安材</v>
+        <v>福建-福州-王忠明</v>
       </c>
       <c r="C192" t="str">
         <v>质检</v>
@@ -3667,15 +3667,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E192" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>2026-07-12 09:12:40</v>
+        <v>2026-07-12 17:25:09</v>
       </c>
       <c r="B193" t="str">
-        <v>江苏南京孙杰</v>
+        <v>辽宁-沈阳-王海青</v>
       </c>
       <c r="C193" t="str">
         <v>质检</v>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>2026-07-12 01:17:41</v>
+        <v>2026-07-12 17:16:28</v>
       </c>
       <c r="B194" t="str">
-        <v>江苏-南京-王玉</v>
+        <v>江苏-苏州-黄迪孟</v>
       </c>
       <c r="C194" t="str">
         <v>质检</v>
@@ -3701,15 +3701,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E194" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>2026-07-12 01:15:07</v>
+        <v>2026-07-12 16:45:02</v>
       </c>
       <c r="B195" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>山东-济南-戴志鹏</v>
       </c>
       <c r="C195" t="str">
         <v>质检</v>
@@ -3718,15 +3718,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E195" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>2026-07-12 01:13:14</v>
+        <v>2026-07-12 16:34:21</v>
       </c>
       <c r="B196" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>湖北-武汉-黄武</v>
       </c>
       <c r="C196" t="str">
         <v>质检</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>2026-07-12 01:12:18</v>
+        <v>2026-07-12 16:25:40</v>
       </c>
       <c r="B197" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C197" t="str">
         <v>质检</v>
@@ -3752,15 +3752,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E197" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>2026-07-12 01:11:38</v>
+        <v>2026-07-12 16:04:05</v>
       </c>
       <c r="B198" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C198" t="str">
         <v>质检</v>
@@ -3769,12 +3769,12 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E198" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>2026-07-12 01:04:52</v>
+        <v>2026-07-12 16:03:47</v>
       </c>
       <c r="B199" t="str">
         <v>广东-深圳-侯晓鹏</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>2026-07-12 00:56:12</v>
+        <v>2026-07-12 15:15:47</v>
       </c>
       <c r="B200" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>河南-郑州-焦威建</v>
       </c>
       <c r="C200" t="str">
         <v>质检</v>
@@ -3803,15 +3803,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E200" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>2026-07-11 20:10:06</v>
+        <v>2026-07-12 14:40:24</v>
       </c>
       <c r="B201" t="str">
-        <v>湖北-武汉-何勇杰</v>
+        <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C201" t="str">
         <v>质检</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>2026-07-11 19:34:39</v>
+        <v>2026-07-12 14:31:08</v>
       </c>
       <c r="B202" t="str">
-        <v>李化学</v>
+        <v>安徽-阜阳-赵子军</v>
       </c>
       <c r="C202" t="str">
         <v>质检</v>
@@ -3837,15 +3837,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E202" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>2026-07-11 19:21:36</v>
+        <v>2026-07-12 12:30:41</v>
       </c>
       <c r="B203" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C203" t="str">
         <v>质检</v>
@@ -3859,10 +3859,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>2026-07-11 19:18:18</v>
+        <v>2026-07-12 12:16:48</v>
       </c>
       <c r="B204" t="str">
-        <v>江苏盐城周婷婷</v>
+        <v>河北-石家庄-赵飞</v>
       </c>
       <c r="C204" t="str">
         <v>质检</v>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>2026-07-11 19:12:34</v>
+        <v>2026-07-12 10:32:13</v>
       </c>
       <c r="B205" t="str">
-        <v>江苏盐城周婷婷</v>
+        <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C205" t="str">
         <v>质检</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>2026-07-11 18:00:12</v>
+        <v>2026-07-12 10:22:55</v>
       </c>
       <c r="B206" t="str">
-        <v>陕西-西安-邵操操</v>
+        <v>四川-成都-程安材</v>
       </c>
       <c r="C206" t="str">
         <v>质检</v>
@@ -3905,15 +3905,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E206" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>2026-07-11 17:59:44</v>
+        <v>2026-07-12 09:12:40</v>
       </c>
       <c r="B207" t="str">
-        <v>陕西-西安-邵操操</v>
+        <v>江苏南京孙杰</v>
       </c>
       <c r="C207" t="str">
         <v>质检</v>
@@ -3922,15 +3922,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E207" t="str">
-        <v>待处理</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>2026-07-11 17:34:29</v>
+        <v>2026-07-12 01:17:41</v>
       </c>
       <c r="B208" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>江苏-南京-王玉</v>
       </c>
       <c r="C208" t="str">
         <v>质检</v>
@@ -3939,15 +3939,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E208" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>2026-07-11 17:33:36</v>
+        <v>2026-07-12 01:15:07</v>
       </c>
       <c r="B209" t="str">
-        <v>江苏-南京-邢希鸣</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C209" t="str">
         <v>质检</v>
@@ -3956,15 +3956,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E209" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>2026-07-11 17:09:25</v>
+        <v>2026-07-12 01:13:14</v>
       </c>
       <c r="B210" t="str">
-        <v>山西-太原-郑连珍</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C210" t="str">
         <v>质检</v>
@@ -3973,15 +3973,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E210" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>2026-07-11 17:09:06</v>
+        <v>2026-07-12 01:12:18</v>
       </c>
       <c r="B211" t="str">
-        <v>安徽-合肥-黄子龙</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C211" t="str">
         <v>质检</v>
@@ -3990,15 +3990,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E211" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>2026-07-11 16:57:16</v>
+        <v>2026-07-12 01:11:38</v>
       </c>
       <c r="B212" t="str">
-        <v>安徽-合肥-彭鹏</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C212" t="str">
         <v>质检</v>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>2026-07-11 16:46:00</v>
+        <v>2026-07-12 01:04:52</v>
       </c>
       <c r="B213" t="str">
-        <v>李化学</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C213" t="str">
         <v>质检</v>
@@ -4024,15 +4024,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E213" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>2026-07-11 15:32:20</v>
+        <v>2026-07-12 00:56:12</v>
       </c>
       <c r="B214" t="str">
-        <v>河南-郑州-王淑豪</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C214" t="str">
         <v>质检</v>
@@ -4041,15 +4041,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E214" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>2026-07-11 15:26:05</v>
+        <v>2026-07-11 20:10:06</v>
       </c>
       <c r="B215" t="str">
-        <v>江西-南昌-胡华波</v>
+        <v>湖北-武汉-何勇杰</v>
       </c>
       <c r="C215" t="str">
         <v>质检</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>2026-07-11 15:07:18</v>
+        <v>2026-07-11 19:34:39</v>
       </c>
       <c r="B216" t="str">
-        <v>李志远</v>
+        <v>李化学</v>
       </c>
       <c r="C216" t="str">
         <v>质检</v>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>2026-07-11 14:33:25</v>
+        <v>2026-07-11 19:21:36</v>
       </c>
       <c r="B217" t="str">
-        <v>辽宁-沈阳-刘海旭</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C217" t="str">
         <v>质检</v>
@@ -4092,15 +4092,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E217" t="str">
-        <v>处理中</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>2026-07-11 14:17:11</v>
+        <v>2026-07-11 19:18:18</v>
       </c>
       <c r="B218" t="str">
-        <v>广东-深圳-侯晓鹏</v>
+        <v>江苏盐城周婷婷</v>
       </c>
       <c r="C218" t="str">
         <v>质检</v>
@@ -4109,15 +4109,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E218" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>2026-07-11 13:48:40</v>
+        <v>2026-07-11 19:12:34</v>
       </c>
       <c r="B219" t="str">
-        <v>郭阳</v>
+        <v>江苏盐城周婷婷</v>
       </c>
       <c r="C219" t="str">
         <v>质检</v>
@@ -4131,10 +4131,10 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>2026-07-11 12:01:11</v>
+        <v>2026-07-11 18:00:12</v>
       </c>
       <c r="B220" t="str">
-        <v>山西-太原-郑连珍</v>
+        <v>陕西-西安-邵操操</v>
       </c>
       <c r="C220" t="str">
         <v>质检</v>
@@ -4143,15 +4143,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E220" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>2026-07-11 12:00:41</v>
+        <v>2026-07-11 17:59:44</v>
       </c>
       <c r="B221" t="str">
-        <v>山西-太原-郑连珍</v>
+        <v>陕西-西安-邵操操</v>
       </c>
       <c r="C221" t="str">
         <v>质检</v>
@@ -4160,15 +4160,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E221" t="str">
-        <v>已处理</v>
+        <v>待处理</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>2026-07-11 12:00:22</v>
+        <v>2026-07-11 17:34:29</v>
       </c>
       <c r="B222" t="str">
-        <v>山西-太原-郑连珍</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C222" t="str">
         <v>质检</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>2026-07-11 09:07:26</v>
+        <v>2026-07-11 17:33:36</v>
       </c>
       <c r="B223" t="str">
-        <v>河北-廊坊-于释尧</v>
+        <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C223" t="str">
         <v>质检</v>
@@ -4194,15 +4194,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E223" t="str">
-        <v>已评价</v>
+        <v>已处理</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>2026-07-11 06:33:54</v>
+        <v>2026-07-11 17:09:25</v>
       </c>
       <c r="B224" t="str">
-        <v>山西-运城-王涛</v>
+        <v>山西-太原-郑连珍</v>
       </c>
       <c r="C224" t="str">
         <v>质检</v>
@@ -4216,10 +4216,10 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>2026-07-11 01:39:12</v>
+        <v>2026-07-11 17:09:06</v>
       </c>
       <c r="B225" t="str">
-        <v>四川-成都-喻忠燕</v>
+        <v>安徽-合肥-黄子龙</v>
       </c>
       <c r="C225" t="str">
         <v>质检</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>2026-07-10 23:47:53</v>
+        <v>2026-07-11 16:57:16</v>
       </c>
       <c r="B226" t="str">
-        <v>安徽合肥王冬冬</v>
+        <v>安徽-合肥-彭鹏</v>
       </c>
       <c r="C226" t="str">
         <v>质检</v>
@@ -4245,15 +4245,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E226" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>2026-07-10 22:47:39</v>
+        <v>2026-07-11 16:46:00</v>
       </c>
       <c r="B227" t="str">
-        <v>广西-南宁-谢礼帆</v>
+        <v>李化学</v>
       </c>
       <c r="C227" t="str">
         <v>质检</v>
@@ -4267,10 +4267,10 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>2026-07-10 22:05:09</v>
+        <v>2026-07-11 15:32:20</v>
       </c>
       <c r="B228" t="str">
-        <v>雷俊</v>
+        <v>河南-郑州-王淑豪</v>
       </c>
       <c r="C228" t="str">
         <v>质检</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>2026-07-10 21:47:12</v>
+        <v>2026-07-11 15:26:05</v>
       </c>
       <c r="B229" t="str">
-        <v>浙江-温州-卢成鹏</v>
+        <v>江西-南昌-胡华波</v>
       </c>
       <c r="C229" t="str">
         <v>质检</v>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>2026-07-10 21:45:42</v>
+        <v>2026-07-11 15:07:18</v>
       </c>
       <c r="B230" t="str">
-        <v>广东-广州-赵华武</v>
+        <v>李志远</v>
       </c>
       <c r="C230" t="str">
         <v>质检</v>
@@ -4318,10 +4318,10 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>2026-07-10 21:37:21</v>
+        <v>2026-07-11 14:33:25</v>
       </c>
       <c r="B231" t="str">
-        <v>江苏-无锡-刘雪伟</v>
+        <v>辽宁-沈阳-刘海旭</v>
       </c>
       <c r="C231" t="str">
         <v>质检</v>
@@ -4330,15 +4330,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E231" t="str">
-        <v>已评价</v>
+        <v>处理中</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>2026-07-10 21:17:50</v>
+        <v>2026-07-11 14:17:11</v>
       </c>
       <c r="B232" t="str">
-        <v>浙江-温州-卢成鹏</v>
+        <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C232" t="str">
         <v>质检</v>
@@ -4347,15 +4347,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E232" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>2026-07-10 21:13:41</v>
+        <v>2026-07-11 13:48:40</v>
       </c>
       <c r="B233" t="str">
-        <v>山西-运城-邵厚华</v>
+        <v>郭阳</v>
       </c>
       <c r="C233" t="str">
         <v>质检</v>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>2026-07-10 21:00:07</v>
+        <v>2026-07-11 12:01:11</v>
       </c>
       <c r="B234" t="str">
-        <v>李化学</v>
+        <v>山西-太原-郑连珍</v>
       </c>
       <c r="C234" t="str">
         <v>质检</v>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>2026-07-10 20:18:49</v>
+        <v>2026-07-11 12:00:41</v>
       </c>
       <c r="B235" t="str">
-        <v>丁凤腾</v>
+        <v>山西-太原-郑连珍</v>
       </c>
       <c r="C235" t="str">
         <v>质检</v>
@@ -4403,10 +4403,10 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>2026-07-10 20:17:37</v>
+        <v>2026-07-11 12:00:22</v>
       </c>
       <c r="B236" t="str">
-        <v>丁凤腾</v>
+        <v>山西-太原-郑连珍</v>
       </c>
       <c r="C236" t="str">
         <v>质检</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>2026-07-10 20:16:33</v>
+        <v>2026-07-11 09:07:26</v>
       </c>
       <c r="B237" t="str">
-        <v>丁凤腾</v>
+        <v>河北-廊坊-于释尧</v>
       </c>
       <c r="C237" t="str">
         <v>质检</v>
@@ -4432,15 +4432,15 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E237" t="str">
-        <v>已处理</v>
+        <v>已评价</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>2026-07-10 20:12:12</v>
+        <v>2026-07-11 06:33:54</v>
       </c>
       <c r="B238" t="str">
-        <v>浙江-杭州-向东</v>
+        <v>山西-运城-王涛</v>
       </c>
       <c r="C238" t="str">
         <v>质检</v>
@@ -4449,556 +4449,12 @@
         <v>质检报告不认可</v>
       </c>
       <c r="E238" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="str">
-        <v>2026-07-10 20:06:22</v>
-      </c>
-      <c r="B239" t="str">
-        <v>山西-太原-闫月翠</v>
-      </c>
-      <c r="C239" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D239" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E239" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="str">
-        <v>2026-07-10 19:41:53</v>
-      </c>
-      <c r="B240" t="str">
-        <v>江西-南昌-王洋</v>
-      </c>
-      <c r="C240" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D240" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E240" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="str">
-        <v>2026-07-10 19:22:29</v>
-      </c>
-      <c r="B241" t="str">
-        <v>安徽-阜阳-彭永光</v>
-      </c>
-      <c r="C241" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D241" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E241" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="str">
-        <v>2026-07-10 19:15:49</v>
-      </c>
-      <c r="B242" t="str">
-        <v>河北-石家庄-汪鹏</v>
-      </c>
-      <c r="C242" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D242" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E242" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="str">
-        <v>2026-07-10 19:14:28</v>
-      </c>
-      <c r="B243" t="str">
-        <v>浙江-杭州-王华山</v>
-      </c>
-      <c r="C243" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D243" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E243" t="str">
-        <v>处理中</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="str">
-        <v>2026-07-10 18:52:53</v>
-      </c>
-      <c r="B244" t="str">
-        <v>李化学</v>
-      </c>
-      <c r="C244" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D244" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E244" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="str">
-        <v>2026-07-10 18:29:37</v>
-      </c>
-      <c r="B245" t="str">
-        <v>李化学</v>
-      </c>
-      <c r="C245" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D245" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E245" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="str">
-        <v>2026-07-10 18:28:53</v>
-      </c>
-      <c r="B246" t="str">
-        <v>李化学</v>
-      </c>
-      <c r="C246" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D246" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E246" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="str">
-        <v>2026-07-10 18:05:03</v>
-      </c>
-      <c r="B247" t="str">
-        <v>李化学</v>
-      </c>
-      <c r="C247" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D247" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E247" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="str">
-        <v>2026-07-10 17:50:25</v>
-      </c>
-      <c r="B248" t="str">
-        <v>河北-石家庄-汪鹏</v>
-      </c>
-      <c r="C248" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D248" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E248" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v>2026-07-10 16:38:25</v>
-      </c>
-      <c r="B249" t="str">
-        <v>山东-东营-刘青文</v>
-      </c>
-      <c r="C249" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D249" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E249" t="str">
-        <v>已评价</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="str">
-        <v>2026-07-10 16:28:50</v>
-      </c>
-      <c r="B250" t="str">
-        <v>广西-南宁-杨帆</v>
-      </c>
-      <c r="C250" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D250" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E250" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="str">
-        <v>2026-07-10 16:23:30</v>
-      </c>
-      <c r="B251" t="str">
-        <v>安徽-芜湖-包飞</v>
-      </c>
-      <c r="C251" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D251" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E251" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="str">
-        <v>2026-07-10 16:14:13</v>
-      </c>
-      <c r="B252" t="str">
-        <v>山东-东营-刘青文</v>
-      </c>
-      <c r="C252" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D252" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E252" t="str">
-        <v>已评价</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="str">
-        <v>2026-07-10 15:22:00</v>
-      </c>
-      <c r="B253" t="str">
-        <v>安徽-合肥-郭琼杰</v>
-      </c>
-      <c r="C253" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D253" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E253" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="str">
-        <v>2026-07-10 15:13:36</v>
-      </c>
-      <c r="B254" t="str">
-        <v>山东-济南-房超</v>
-      </c>
-      <c r="C254" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D254" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E254" t="str">
-        <v>已评价</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="str">
-        <v>2026-07-10 15:03:28</v>
-      </c>
-      <c r="B255" t="str">
-        <v>四川-成都-王何意</v>
-      </c>
-      <c r="C255" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D255" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E255" t="str">
-        <v>处理中</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="str">
-        <v>2026-07-10 14:53:04</v>
-      </c>
-      <c r="B256" t="str">
-        <v>河南-商丘-陈玉兰</v>
-      </c>
-      <c r="C256" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D256" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E256" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="str">
-        <v>2026-07-10 14:28:44</v>
-      </c>
-      <c r="B257" t="str">
-        <v>安徽-合肥-古月</v>
-      </c>
-      <c r="C257" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D257" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E257" t="str">
-        <v>已评价</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="str">
-        <v>2026-07-10 14:23:47</v>
-      </c>
-      <c r="B258" t="str">
-        <v>广东-深圳-陈敬丽</v>
-      </c>
-      <c r="C258" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D258" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E258" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="str">
-        <v>2026-07-10 14:22:28</v>
-      </c>
-      <c r="B259" t="str">
-        <v>广东-深圳-陈敬丽</v>
-      </c>
-      <c r="C259" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D259" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E259" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="str">
-        <v>2026-07-10 13:43:47</v>
-      </c>
-      <c r="B260" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
-      </c>
-      <c r="C260" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D260" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E260" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="str">
-        <v>2026-07-10 13:38:31</v>
-      </c>
-      <c r="B261" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
-      </c>
-      <c r="C261" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D261" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E261" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="str">
-        <v>2026-07-10 13:37:30</v>
-      </c>
-      <c r="B262" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
-      </c>
-      <c r="C262" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D262" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E262" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="str">
-        <v>2026-07-10 13:36:46</v>
-      </c>
-      <c r="B263" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
-      </c>
-      <c r="C263" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D263" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E263" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="str">
-        <v>2026-07-10 13:35:16</v>
-      </c>
-      <c r="B264" t="str">
-        <v>江苏-苏州-杨鲁攀</v>
-      </c>
-      <c r="C264" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D264" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E264" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="str">
-        <v>2026-07-10 12:43:49</v>
-      </c>
-      <c r="B265" t="str">
-        <v>安徽-合肥-李勇</v>
-      </c>
-      <c r="C265" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D265" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E265" t="str">
-        <v>已评价</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="str">
-        <v>2026-07-10 12:31:29</v>
-      </c>
-      <c r="B266" t="str">
-        <v>广东-深圳-陈敬丽</v>
-      </c>
-      <c r="C266" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D266" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E266" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="str">
-        <v>2026-07-10 12:24:09</v>
-      </c>
-      <c r="B267" t="str">
-        <v>广东-深圳-陈敬丽</v>
-      </c>
-      <c r="C267" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D267" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E267" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="str">
-        <v>2026-07-10 11:17:26</v>
-      </c>
-      <c r="B268" t="str">
-        <v>天津-天津-肖显阳</v>
-      </c>
-      <c r="C268" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D268" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E268" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>2026-07-10 11:06:07</v>
-      </c>
-      <c r="B269" t="str">
-        <v>江西-南昌-杨昌鹏</v>
-      </c>
-      <c r="C269" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D269" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E269" t="str">
-        <v>已处理</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="str">
-        <v>2026-07-10 10:42:29</v>
-      </c>
-      <c r="B270" t="str">
-        <v>山西-太原-闫月翠</v>
-      </c>
-      <c r="C270" t="str">
-        <v>质检</v>
-      </c>
-      <c r="D270" t="str">
-        <v>质检报告不认可</v>
-      </c>
-      <c r="E270" t="str">
         <v>已处理</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E270"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E238"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/商户反馈近7天.xlsx
+++ b/商户反馈近7天.xlsx
@@ -397,13 +397,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E238"/>
+  <dimension ref="A1:I238"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -414,13 +418,25 @@
         <v>商户名称</v>
       </c>
       <c r="C1" t="str">
+        <v>质检码</v>
+      </c>
+      <c r="D1" t="str">
+        <v>IMEI</v>
+      </c>
+      <c r="E1" t="str">
+        <v>商品标题</v>
+      </c>
+      <c r="F1" t="str">
         <v>一级分类</v>
       </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
         <v>二级分类</v>
       </c>
-      <c r="E1" t="str">
+      <c r="H1" t="str">
         <v>状态</v>
+      </c>
+      <c r="I1" t="str">
+        <v>类目</v>
       </c>
     </row>
     <row r="2">
@@ -431,13 +447,25 @@
         <v>江苏-南通-刘鑫</v>
       </c>
       <c r="C2" t="str">
-        <v>质检</v>
+        <v>1213463558</v>
       </c>
       <c r="D2" t="str">
-        <v>质检报告不认可</v>
+        <v>353170666136324</v>
       </c>
       <c r="E2" t="str">
+        <v>苹果 iPhone 17 Pro Max</v>
+      </c>
+      <c r="F2" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G2" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H2" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I2" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="3">
@@ -448,13 +476,25 @@
         <v>广东-深圳-苏宇晖</v>
       </c>
       <c r="C3" t="str">
-        <v>质检</v>
+        <v>1211535515</v>
       </c>
       <c r="D3" t="str">
-        <v>质检报告不认可</v>
+        <v>YNVJJQ24CP</v>
       </c>
       <c r="E3" t="str">
+        <v>智能手表 8新 苹果 Apple Watch Series 7 32G 星光色 二手优品</v>
+      </c>
+      <c r="F3" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G3" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H3" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I3" t="str">
+        <v>智能手表</v>
       </c>
     </row>
     <row r="4">
@@ -465,13 +505,25 @@
         <v>四川-成都-吕霞</v>
       </c>
       <c r="C4" t="str">
-        <v>质检</v>
+        <v>1213482462</v>
       </c>
       <c r="D4" t="str">
-        <v>质检报告不认可</v>
+        <v>868833054493155</v>
       </c>
       <c r="E4" t="str">
+        <v>vivo iQOO 7</v>
+      </c>
+      <c r="F4" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G4" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H4" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I4" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="5">
@@ -482,13 +534,25 @@
         <v>重庆-徐若鸿</v>
       </c>
       <c r="C5" t="str">
-        <v>质检</v>
+        <v>1213528696</v>
       </c>
       <c r="D5" t="str">
-        <v>质检报告不认可</v>
+        <v>862751050162234</v>
       </c>
       <c r="E5" t="str">
+        <v>华为 Mate 40 Pro (5G)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G5" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H5" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I5" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="6">
@@ -499,13 +563,25 @@
         <v>李化学</v>
       </c>
       <c r="C6" t="str">
-        <v>质检</v>
+        <v>1213532280</v>
       </c>
       <c r="D6" t="str">
-        <v>质检报告不认可</v>
+        <v>863316043235650</v>
       </c>
       <c r="E6" t="str">
+        <v>vivo S6</v>
+      </c>
+      <c r="F6" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G6" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H6" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I6" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="7">
@@ -516,13 +592,25 @@
         <v>江苏-南京-许国军</v>
       </c>
       <c r="C7" t="str">
-        <v>质检</v>
+        <v>1213464131</v>
       </c>
       <c r="D7" t="str">
-        <v>质检报告不认可</v>
+        <v>354869722853579</v>
       </c>
       <c r="E7" t="str">
+        <v>手机 9新 苹果 iPhone 13 Pro Max 128G 银色 二手优品</v>
+      </c>
+      <c r="F7" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G7" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H7" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I7" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="8">
@@ -533,13 +621,25 @@
         <v>天津张扬</v>
       </c>
       <c r="C8" t="str">
-        <v>质检</v>
+        <v>1213503135</v>
       </c>
       <c r="D8" t="str">
-        <v>质检报告不认可</v>
+        <v>861558088293092</v>
       </c>
       <c r="E8" t="str">
+        <v>OPPO K13 Turbo Pro</v>
+      </c>
+      <c r="F8" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G8" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H8" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I8" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="9">
@@ -550,13 +650,25 @@
         <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C9" t="str">
-        <v>质检</v>
+        <v>1213490135</v>
       </c>
       <c r="D9" t="str">
-        <v>质检报告不认可</v>
+        <v>860323053551380</v>
       </c>
       <c r="E9" t="str">
+        <v>手机 95新 华为 华为 Mate 40 Pro (4G) 8GB+256G 亮黑色 二手优品</v>
+      </c>
+      <c r="F9" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G9" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H9" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I9" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +679,25 @@
         <v>江苏-南京-陈永祯</v>
       </c>
       <c r="C10" t="str">
-        <v>质检</v>
+        <v>1000470497</v>
       </c>
       <c r="D10" t="str">
-        <v>质检报告不认可</v>
+        <v>359456333382480</v>
       </c>
       <c r="E10" t="str">
+        <v>手机 95新 苹果 iPhone 17 Pro Max 256G 星宇橙色 二手优品</v>
+      </c>
+      <c r="F10" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G10" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H10" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I10" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="11">
@@ -584,13 +708,25 @@
         <v>江苏-南通-马志豪</v>
       </c>
       <c r="C11" t="str">
-        <v>质检</v>
+        <v>1213463270</v>
       </c>
       <c r="D11" t="str">
-        <v>质检报告不认可</v>
+        <v>359877771259692</v>
       </c>
       <c r="E11" t="str">
+        <v>苹果 iPhone 17 Pro</v>
+      </c>
+      <c r="F11" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G11" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H11" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I11" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="12">
@@ -601,13 +737,25 @@
         <v>江西-南昌-张小明</v>
       </c>
       <c r="C12" t="str">
-        <v>质检</v>
+        <v>1213490260</v>
       </c>
       <c r="D12" t="str">
-        <v>质检报告不认可</v>
+        <v>860819089643698</v>
       </c>
       <c r="E12" t="str">
+        <v>手机 9新 一加 一加 Ace 6T 16GB+256G 闪速黑 二手优品</v>
+      </c>
+      <c r="F12" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G12" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H12" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I12" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="13">
@@ -618,13 +766,25 @@
         <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C13" t="str">
-        <v>质检</v>
+        <v>1213490123</v>
       </c>
       <c r="D13" t="str">
-        <v>质检报告不认可</v>
+        <v>860079055544921</v>
       </c>
       <c r="E13" t="str">
+        <v>手机 7新以下 红米 红米 Note 9 (4G) 8GB+128G 羽墨黑 二手优品</v>
+      </c>
+      <c r="F13" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G13" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H13" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I13" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="14">
@@ -635,13 +795,25 @@
         <v>安徽-合肥-李怀志</v>
       </c>
       <c r="C14" t="str">
-        <v>质检</v>
+        <v>1211937604</v>
       </c>
       <c r="D14" t="str">
-        <v>质检报告不认可</v>
+        <v>867574071077503</v>
       </c>
       <c r="E14" t="str">
+        <v>手机 7新以下 红米 红米 Note 13R 6GB+128G 冰晶银 二手优品</v>
+      </c>
+      <c r="F14" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G14" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H14" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I14" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="15">
@@ -652,13 +824,25 @@
         <v>河南-郑州-黄倩</v>
       </c>
       <c r="C15" t="str">
-        <v>质检</v>
+        <v>1213503876</v>
       </c>
       <c r="D15" t="str">
-        <v>质检报告不认可</v>
+        <v>356155609786860</v>
       </c>
       <c r="E15" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 苹果 iPhone 14 128G 午夜色 二手优品</v>
+      </c>
+      <c r="F15" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G15" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H15" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I15" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="16">
@@ -669,13 +853,25 @@
         <v>山东-济南-董其泽</v>
       </c>
       <c r="C16" t="str">
-        <v>质检</v>
+        <v>1213131369</v>
       </c>
       <c r="D16" t="str">
-        <v>质检报告不认可</v>
+        <v>357649608955319</v>
       </c>
       <c r="E16" t="str">
-        <v>已处理</v>
+        <v>手机 7新 苹果 iPhone 14 256G 星光色 二手优品</v>
+      </c>
+      <c r="F16" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G16" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H16" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I16" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="17">
@@ -686,13 +882,25 @@
         <v>云南-昆明-刘芳强</v>
       </c>
       <c r="C17" t="str">
-        <v>质检</v>
+        <v>1213420963</v>
       </c>
       <c r="D17" t="str">
-        <v>质检报告不认可</v>
+        <v>863821086299885</v>
       </c>
       <c r="E17" t="str">
+        <v>华为 Mate 70 Pro</v>
+      </c>
+      <c r="F17" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G17" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H17" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I17" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="18">
@@ -703,13 +911,25 @@
         <v>云南-昆明-刘芳强</v>
       </c>
       <c r="C18" t="str">
-        <v>质检</v>
+        <v>1213420965</v>
       </c>
       <c r="D18" t="str">
-        <v>质检报告不认可</v>
+        <v>864910084617716</v>
       </c>
       <c r="E18" t="str">
+        <v>华为 畅享 90 Pro Max</v>
+      </c>
+      <c r="F18" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G18" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H18" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I18" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="19">
@@ -720,13 +940,25 @@
         <v>丁凤腾</v>
       </c>
       <c r="C19" t="str">
-        <v>质检</v>
+        <v>1213420808</v>
       </c>
       <c r="D19" t="str">
-        <v>质检报告不认可</v>
+        <v>353656197174545</v>
       </c>
       <c r="E19" t="str">
+        <v>手机 95新 苹果 iPhone 14 Plus 256G 星光色 二手优品</v>
+      </c>
+      <c r="F19" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G19" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H19" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I19" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="20">
@@ -737,13 +969,25 @@
         <v>浙江-金华-吴健鋆</v>
       </c>
       <c r="C20" t="str">
-        <v>质检</v>
+        <v>1213471657</v>
       </c>
       <c r="D20" t="str">
-        <v>质检报告不认可</v>
+        <v>866014079422352</v>
       </c>
       <c r="E20" t="str">
+        <v>手机 7新以下 OPPO OPPO Find X8 Ultra 卫星通信版 16GB+1T 月光白 二手优品</v>
+      </c>
+      <c r="F20" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G20" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H20" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I20" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="21">
@@ -754,13 +998,25 @@
         <v>浙江-杭州-方来</v>
       </c>
       <c r="C21" t="str">
-        <v>质检</v>
+        <v>1005932678</v>
       </c>
       <c r="D21" t="str">
-        <v>质检报告不认可</v>
+        <v>GWYCQE13JQH3</v>
       </c>
       <c r="E21" t="str">
+        <v>耳机/耳麦 7新以下 苹果 Apple AirPods Pro 一代 （单耳） 白色 二手优品</v>
+      </c>
+      <c r="F21" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G21" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H21" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I21" t="str">
+        <v>耳机/耳麦</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +1027,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C22" t="str">
-        <v>质检</v>
+        <v>1213466633</v>
       </c>
       <c r="D22" t="str">
-        <v>质检报告不认可</v>
+        <v>L621519000112F940060</v>
       </c>
       <c r="E22" t="str">
-        <v>已处理</v>
+        <v>平板电脑 7新 OPPO OPPO Pad 5 柔光版 12.1英寸 12GB+256G 幸运紫 二手优品</v>
+      </c>
+      <c r="F22" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G22" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H22" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I22" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="23">
@@ -788,13 +1056,25 @@
         <v>江西南昌聂宇杰</v>
       </c>
       <c r="C23" t="str">
-        <v>质检</v>
+        <v>1213498755</v>
       </c>
       <c r="D23" t="str">
-        <v>质检报告不认可</v>
+        <v>866550073538016</v>
       </c>
       <c r="E23" t="str">
-        <v>已处理</v>
+        <v>vivo X100s</v>
+      </c>
+      <c r="F23" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G23" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H23" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I23" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="24">
@@ -805,13 +1085,25 @@
         <v>安徽合肥王冬冬</v>
       </c>
       <c r="C24" t="str">
-        <v>质检</v>
+        <v>1212385514</v>
       </c>
       <c r="D24" t="str">
-        <v>质检报告不认可</v>
+        <v>863342047832490</v>
       </c>
       <c r="E24" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 华为 华为 Mate 40 Pro (5G) 8GB+256G 秋日胡杨 二手优品</v>
+      </c>
+      <c r="F24" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G24" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H24" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I24" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="25">
@@ -822,13 +1114,25 @@
         <v>广东佛山孟吉祥</v>
       </c>
       <c r="C25" t="str">
-        <v>质检</v>
+        <v>1213448024</v>
       </c>
       <c r="D25" t="str">
-        <v>质检报告不认可</v>
+        <v>863552089476127</v>
       </c>
       <c r="E25" t="str">
-        <v>已处理</v>
+        <v>红米 Note 15</v>
+      </c>
+      <c r="F25" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G25" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H25" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I25" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="26">
@@ -839,13 +1143,25 @@
         <v>山东-济南-董其泽</v>
       </c>
       <c r="C26" t="str">
-        <v>质检</v>
+        <v>1212908691</v>
       </c>
       <c r="D26" t="str">
-        <v>质检报告不认可</v>
+        <v>357649607651034</v>
       </c>
       <c r="E26" t="str">
-        <v>已处理</v>
+        <v>手机 7新 苹果 iPhone 14 512G 午夜色 BS机</v>
+      </c>
+      <c r="F26" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G26" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H26" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I26" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="27">
@@ -856,13 +1172,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C27" t="str">
-        <v>质检</v>
+        <v>1213433788</v>
       </c>
       <c r="D27" t="str">
-        <v>质检报告不认可</v>
+        <v>354702290395519</v>
       </c>
       <c r="E27" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 三星 三星 Galaxy Z Flip5 8GB+512G 冰薄荷 二手优品</v>
+      </c>
+      <c r="F27" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G27" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H27" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I27" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="28">
@@ -873,13 +1201,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C28" t="str">
-        <v>质检</v>
+        <v>1213433786</v>
       </c>
       <c r="D28" t="str">
-        <v>质检报告不认可</v>
+        <v>865590060334954</v>
       </c>
       <c r="E28" t="str">
+        <v>手机 7新以下 努比亚 努比亚 红魔 8 Pro+ 16GB+512G 暗夜骑士 二手优品</v>
+      </c>
+      <c r="F28" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G28" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H28" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I28" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="29">
@@ -890,13 +1230,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C29" t="str">
-        <v>质检</v>
+        <v>1213433792</v>
       </c>
       <c r="D29" t="str">
-        <v>质检报告不认可</v>
+        <v>867892068946070</v>
       </c>
       <c r="E29" t="str">
+        <v>手机 7新以下 一加 一加 12 12GB+256G 岩黑 二手优品</v>
+      </c>
+      <c r="F29" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G29" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H29" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I29" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="30">
@@ -907,13 +1259,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C30" t="str">
-        <v>质检</v>
+        <v>1213433791</v>
       </c>
       <c r="D30" t="str">
-        <v>质检报告不认可</v>
+        <v>860073066998499</v>
       </c>
       <c r="E30" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 OPPO OPPO Find X6 12GB+256G 飞泉绿 二手优品</v>
+      </c>
+      <c r="F30" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G30" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H30" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I30" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="31">
@@ -924,13 +1288,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C31" t="str">
-        <v>质检</v>
+        <v>1213433794</v>
       </c>
       <c r="D31" t="str">
-        <v>质检报告不认可</v>
+        <v>865288069050214</v>
       </c>
       <c r="E31" t="str">
+        <v>手机 7新以下 一加 一加 Ace 12GB+512G 开黑 二手优品</v>
+      </c>
+      <c r="F31" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G31" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H31" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I31" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="32">
@@ -941,13 +1317,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C32" t="str">
-        <v>质检</v>
+        <v>1008415062</v>
       </c>
       <c r="D32" t="str">
-        <v>质检报告不认可</v>
+        <v>357120489492020</v>
       </c>
       <c r="E32" t="str">
+        <v>手机 95新 三星 三星 Galaxy Z Flip5 8GB+256G 云影灰 二手优品</v>
+      </c>
+      <c r="F32" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G32" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H32" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I32" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="33">
@@ -958,13 +1346,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C33" t="str">
-        <v>质检</v>
+        <v>1007165520</v>
       </c>
       <c r="D33" t="str">
-        <v>质检报告不认可</v>
+        <v>868233039232614</v>
       </c>
       <c r="E33" t="str">
+        <v>手机 一加 一加 5T 8GB+128G 熔岩红 二手优品</v>
+      </c>
+      <c r="F33" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G33" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H33" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I33" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="34">
@@ -975,13 +1375,25 @@
         <v>山东-济南-董其泽</v>
       </c>
       <c r="C34" t="str">
-        <v>质检</v>
+        <v>1212931815</v>
       </c>
       <c r="D34" t="str">
-        <v>质检报告不认可</v>
+        <v>357684391765039</v>
       </c>
       <c r="E34" t="str">
-        <v>已处理</v>
+        <v>手机 7新 苹果 iPhone 14 256G 蓝色 二手优品</v>
+      </c>
+      <c r="F34" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G34" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H34" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I34" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="35">
@@ -992,13 +1404,25 @@
         <v>山东-济南-薛亚伟</v>
       </c>
       <c r="C35" t="str">
-        <v>质检</v>
+        <v>1213422489</v>
       </c>
       <c r="D35" t="str">
-        <v>质检报告不认可</v>
+        <v>862230072767973</v>
       </c>
       <c r="E35" t="str">
+        <v>手机 99新 魅族 魅族 21 Note 16GB+256G 魅族白 二手优品</v>
+      </c>
+      <c r="F35" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G35" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H35" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I35" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="36">
@@ -1009,13 +1433,25 @@
         <v>湖北-武汉-李俊杰</v>
       </c>
       <c r="C36" t="str">
-        <v>质检</v>
+        <v>1213420950</v>
       </c>
       <c r="D36" t="str">
-        <v>质检报告不认可</v>
+        <v>355871450527937</v>
       </c>
       <c r="E36" t="str">
+        <v>手机 7新以下 苹果 iPhone 16 256G 黑色 二手优品</v>
+      </c>
+      <c r="F36" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G36" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H36" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I36" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="37">
@@ -1026,13 +1462,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C37" t="str">
-        <v>质检</v>
+        <v>1213249847</v>
       </c>
       <c r="D37" t="str">
-        <v>质检报告不认可</v>
+        <v>L632003000153G6N0026</v>
       </c>
       <c r="E37" t="str">
+        <v>平板电脑 95新 一加 一加 平板 11.61英寸 12GB+256G 苔原绿 二手优品</v>
+      </c>
+      <c r="F37" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G37" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H37" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I37" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="38">
@@ -1043,13 +1491,25 @@
         <v>辽宁-大连-郭浩</v>
       </c>
       <c r="C38" t="str">
-        <v>质检</v>
+        <v>1213394006</v>
       </c>
       <c r="D38" t="str">
-        <v>质检报告不认可</v>
+        <v>862742065550869</v>
       </c>
       <c r="E38" t="str">
-        <v>已处理</v>
+        <v>红米 Note 11T Pro</v>
+      </c>
+      <c r="F38" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G38" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H38" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I38" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="39">
@@ -1060,13 +1520,25 @@
         <v>江苏-南京-冯卯</v>
       </c>
       <c r="C39" t="str">
-        <v>质检</v>
+        <v>1213416961</v>
       </c>
       <c r="D39" t="str">
-        <v>质检报告不认可</v>
+        <v>S7NRKD019382309</v>
       </c>
       <c r="E39" t="str">
+        <v xml:space="preserve">笔记本 7新以下 华硕 华硕 天选 5 Pro 日蚀灰 </v>
+      </c>
+      <c r="F39" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G39" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H39" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I39" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="40">
@@ -1077,13 +1549,25 @@
         <v>安徽-合肥-陈旭</v>
       </c>
       <c r="C40" t="str">
-        <v>质检</v>
+        <v>1213154532</v>
       </c>
       <c r="D40" t="str">
-        <v>质检报告不认可</v>
+        <v>356967345628903</v>
       </c>
       <c r="E40" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 14 Pro Max</v>
+      </c>
+      <c r="F40" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G40" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H40" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I40" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="41">
@@ -1094,13 +1578,25 @@
         <v>吉林-长春-王彦文</v>
       </c>
       <c r="C41" t="str">
-        <v>质检</v>
+        <v>1213413762</v>
       </c>
       <c r="D41" t="str">
-        <v>质检报告不认可</v>
+        <v>864300071635626</v>
       </c>
       <c r="E41" t="str">
-        <v>已处理</v>
+        <v>红米 15R 5G</v>
+      </c>
+      <c r="F41" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G41" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H41" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I41" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="42">
@@ -1111,13 +1607,25 @@
         <v>江苏-南京-冯卯</v>
       </c>
       <c r="C42" t="str">
-        <v>质检</v>
+        <v>1213416964</v>
       </c>
       <c r="D42" t="str">
-        <v>质检报告不认可</v>
+        <v>N1NRCX122756043</v>
       </c>
       <c r="E42" t="str">
+        <v xml:space="preserve">笔记本 7新以下 华硕 华硕 天选 3 日蚀灰 </v>
+      </c>
+      <c r="F42" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G42" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H42" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I42" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="43">
@@ -1128,13 +1636,25 @@
         <v>黑龙江-哈尔滨-李士静</v>
       </c>
       <c r="C43" t="str">
-        <v>质检</v>
+        <v>1213373277</v>
       </c>
       <c r="D43" t="str">
-        <v>质检报告不认可</v>
+        <v>866556075721740</v>
       </c>
       <c r="E43" t="str">
-        <v>已处理</v>
+        <v>华为 Mate 60 Pro+</v>
+      </c>
+      <c r="F43" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G43" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H43" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I43" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="44">
@@ -1145,13 +1665,25 @@
         <v>辽宁-沈阳-姜闯</v>
       </c>
       <c r="C44" t="str">
-        <v>质检</v>
+        <v>1213422057</v>
       </c>
       <c r="D44" t="str">
-        <v>质检报告不认可</v>
+        <v>868861070076936</v>
       </c>
       <c r="E44" t="str">
-        <v>已处理</v>
+        <v>华为 Mate 60</v>
+      </c>
+      <c r="F44" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G44" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H44" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I44" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="45">
@@ -1162,13 +1694,25 @@
         <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C45" t="str">
-        <v>质检</v>
+        <v>1213325651</v>
       </c>
       <c r="D45" t="str">
-        <v>质检报告不认可</v>
+        <v>358666977176292</v>
       </c>
       <c r="E45" t="str">
+        <v>苹果 iPhone 14 Pro</v>
+      </c>
+      <c r="F45" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G45" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H45" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I45" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="46">
@@ -1179,13 +1723,25 @@
         <v>江西-南昌-张小明</v>
       </c>
       <c r="C46" t="str">
-        <v>质检</v>
+        <v>1213317026</v>
       </c>
       <c r="D46" t="str">
-        <v>质检报告不认可</v>
+        <v>866771075509496</v>
       </c>
       <c r="E46" t="str">
+        <v>手机 95新 vivo vivo iQOO Z10 Turbo Pro 12GB+256G 云海白 二手优品</v>
+      </c>
+      <c r="F46" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G46" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H46" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I46" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="47">
@@ -1196,13 +1752,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C47" t="str">
-        <v>质检</v>
+        <v>1213249851</v>
       </c>
       <c r="D47" t="str">
-        <v>质检报告不认可</v>
+        <v>400F9C007T0000A</v>
       </c>
       <c r="E47" t="str">
+        <v>平板电脑 95新 vivo vivo Pad 3 Pro 13.0英寸 12GB+256G 春潮蓝 二手优品</v>
+      </c>
+      <c r="F47" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G47" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H47" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I47" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="48">
@@ -1213,13 +1781,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C48" t="str">
-        <v>质检</v>
+        <v>1213249845</v>
       </c>
       <c r="D48" t="str">
-        <v>质检报告不认可</v>
+        <v>400FAR00320000A</v>
       </c>
       <c r="E48" t="str">
+        <v>平板电脑 95新 vivo vivo Pad 3 Pro 13.0英寸 12GB+256G 寒星灰 二手优品</v>
+      </c>
+      <c r="F48" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G48" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H48" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I48" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="49">
@@ -1230,13 +1810,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C49" t="str">
-        <v>质检</v>
+        <v>1213249844</v>
       </c>
       <c r="D49" t="str">
-        <v>质检报告不认可</v>
+        <v>400F9C000U0000A</v>
       </c>
       <c r="E49" t="str">
+        <v>平板电脑 95新 vivo vivo Pad 3 Pro 13.0英寸 12GB+256G 寒星灰 二手优品</v>
+      </c>
+      <c r="F49" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G49" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H49" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I49" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="50">
@@ -1247,13 +1839,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C50" t="str">
-        <v>质检</v>
+        <v>1213249830</v>
       </c>
       <c r="D50" t="str">
-        <v>质检报告不认可</v>
+        <v>72272/05W504129</v>
       </c>
       <c r="E50" t="str">
+        <v>平板电脑 95新 小米 小米 Pad 8 Pro 柔光版 11.2英寸 12GB+256G 冰晶蓝 展示机</v>
+      </c>
+      <c r="F50" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G50" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H50" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I50" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="51">
@@ -1264,13 +1868,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C51" t="str">
-        <v>质检</v>
+        <v>1213249831</v>
       </c>
       <c r="D51" t="str">
-        <v>质检报告不认可</v>
+        <v>71787/05WN01017</v>
       </c>
       <c r="E51" t="str">
+        <v>平板电脑 99新 小米 小米 Pad 8 Pro 柔光版 11.2英寸 12GB+256G 冰晶蓝 二手优品</v>
+      </c>
+      <c r="F51" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G51" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H51" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I51" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="52">
@@ -1281,13 +1897,25 @@
         <v>云南-玉溪-吴正伟</v>
       </c>
       <c r="C52" t="str">
-        <v>质检</v>
+        <v>1213384025</v>
       </c>
       <c r="D52" t="str">
-        <v>质检报告不认可</v>
+        <v>CNQD4JR3YG</v>
       </c>
       <c r="E52" t="str">
+        <v>苹果 iPad Air6 (2024) 13.0英寸</v>
+      </c>
+      <c r="F52" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G52" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H52" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I52" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="53">
@@ -1298,13 +1926,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C53" t="str">
-        <v>质检</v>
+        <v>1213249827</v>
       </c>
       <c r="D53" t="str">
-        <v>质检报告不认可</v>
+        <v>L632003000152G6NO04U</v>
       </c>
       <c r="E53" t="str">
+        <v>平板电脑 7新以下 一加 一加 平板 11.61英寸 8GB+256G 苔原绿 二手优品</v>
+      </c>
+      <c r="F53" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G53" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H53" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I53" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="54">
@@ -1315,13 +1955,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C54" t="str">
-        <v>质检</v>
+        <v>1213249848</v>
       </c>
       <c r="D54" t="str">
-        <v>质检报告不认可</v>
+        <v>L632003000147GGN004N</v>
       </c>
       <c r="E54" t="str">
+        <v>平板电脑 7新以下 一加 一加 平板 11.61英寸 8GB+256G 深空灰 二手优品</v>
+      </c>
+      <c r="F54" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G54" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H54" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I54" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="55">
@@ -1332,13 +1984,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C55" t="str">
-        <v>质检</v>
+        <v>1213249837</v>
       </c>
       <c r="D55" t="str">
-        <v>质检报告不认可</v>
+        <v>860357067713977</v>
       </c>
       <c r="E55" t="str">
+        <v>手机 7新以下 OPPO OPPO Find N2 Flip 8GB+256G 慕紫 二手优品</v>
+      </c>
+      <c r="F55" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G55" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H55" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I55" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="56">
@@ -1349,13 +2013,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C56" t="str">
-        <v>质检</v>
+        <v>1213249828</v>
       </c>
       <c r="D56" t="str">
-        <v>质检报告不认可</v>
+        <v>L632001000348F9C0108</v>
       </c>
       <c r="E56" t="str">
-        <v>已处理</v>
+        <v>平板电脑 8新 OPPO OPPO Pad 5 12.1英寸 12GB+256G 星河银 二手优品</v>
+      </c>
+      <c r="F56" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G56" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H56" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I56" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="57">
@@ -1366,13 +2042,25 @@
         <v>广东佛山孟吉祥</v>
       </c>
       <c r="C57" t="str">
-        <v>质检</v>
+        <v>1213325417</v>
       </c>
       <c r="D57" t="str">
-        <v>质检报告不认可</v>
+        <v>860613077623659</v>
       </c>
       <c r="E57" t="str">
-        <v>已处理</v>
+        <v>荣耀 GT</v>
+      </c>
+      <c r="F57" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G57" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H57" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I57" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="58">
@@ -1383,13 +2071,25 @@
         <v>江西-南昌-涂荣志</v>
       </c>
       <c r="C58" t="str">
-        <v>质检</v>
+        <v>1213311491</v>
       </c>
       <c r="D58" t="str">
-        <v>质检报告不认可</v>
+        <v>862646088174427</v>
       </c>
       <c r="E58" t="str">
+        <v>手机 9新 红米 红米 K90 12GB+512G 水蓝色 二手优品</v>
+      </c>
+      <c r="F58" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G58" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H58" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I58" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="59">
@@ -1400,13 +2100,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C59" t="str">
-        <v>质检</v>
+        <v>1213249823</v>
       </c>
       <c r="D59" t="str">
-        <v>质检报告不认可</v>
+        <v>400FAR00100000A</v>
       </c>
       <c r="E59" t="str">
-        <v>已处理</v>
+        <v>平板电脑 8新 vivo vivo Pad 3 Pro 13.0英寸 12GB+256G 春潮蓝 二手优品</v>
+      </c>
+      <c r="F59" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G59" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H59" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I59" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="60">
@@ -1417,13 +2129,25 @@
         <v>浙江-金华-吴健鋆</v>
       </c>
       <c r="C60" t="str">
-        <v>质检</v>
+        <v>1213328422</v>
       </c>
       <c r="D60" t="str">
-        <v>质检报告不认可</v>
+        <v>868040077529375</v>
       </c>
       <c r="E60" t="str">
+        <v>手机 7新以下 华为 华为 Mate 70 RS 非凡大师 16GB+1T 皓白 二手优品</v>
+      </c>
+      <c r="F60" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G60" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H60" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I60" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="61">
@@ -1434,13 +2158,25 @@
         <v>江苏-南京-冯卯</v>
       </c>
       <c r="C61" t="str">
-        <v>质检</v>
+        <v>1213394889</v>
       </c>
       <c r="D61" t="str">
-        <v>质检报告不认可</v>
+        <v>121339488900000</v>
       </c>
       <c r="E61" t="str">
+        <v xml:space="preserve">笔记本 7新以下 联想 联想 拯救者 Y9000P 2023 碳晶灰 </v>
+      </c>
+      <c r="F61" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G61" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H61" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I61" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="62">
@@ -1451,13 +2187,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C62" t="str">
-        <v>质检</v>
+        <v>1213264313</v>
       </c>
       <c r="D62" t="str">
-        <v>质检报告不认可</v>
+        <v>868952079641844</v>
       </c>
       <c r="E62" t="str">
+        <v>华为 Mate X6 典藏版</v>
+      </c>
+      <c r="F62" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G62" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H62" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I62" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="63">
@@ -1468,13 +2216,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C63" t="str">
-        <v>质检</v>
+        <v>1213264314</v>
       </c>
       <c r="D63" t="str">
-        <v>质检报告不认可</v>
+        <v>866053071313193</v>
       </c>
       <c r="E63" t="str">
+        <v>华为 Pura 70 Ultra</v>
+      </c>
+      <c r="F63" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G63" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H63" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I63" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="64">
@@ -1485,13 +2245,25 @@
         <v>河南-安阳-徐晓</v>
       </c>
       <c r="C64" t="str">
-        <v>质检</v>
+        <v>1213325482</v>
       </c>
       <c r="D64" t="str">
-        <v>质检报告不认可</v>
+        <v>869918073768320</v>
       </c>
       <c r="E64" t="str">
-        <v>已处理</v>
+        <v>华为 Mate 60</v>
+      </c>
+      <c r="F64" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G64" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H64" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I64" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="65">
@@ -1502,13 +2274,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C65" t="str">
-        <v>质检</v>
+        <v>1213249836</v>
       </c>
       <c r="D65" t="str">
-        <v>质检报告不认可</v>
+        <v>867485085293731</v>
       </c>
       <c r="E65" t="str">
-        <v>已处理</v>
+        <v>手机 95新 一加 一加 Ace 6 16GB+256G 闪白 二手优品</v>
+      </c>
+      <c r="F65" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G65" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H65" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I65" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="66">
@@ -1519,13 +2303,25 @@
         <v>福建-福州-林明铿</v>
       </c>
       <c r="C66" t="str">
-        <v>质检</v>
+        <v>1009958157</v>
       </c>
       <c r="D66" t="str">
-        <v>质检报告不认可</v>
+        <v>350635391340949</v>
       </c>
       <c r="E66" t="str">
+        <v>手机 7新 苹果 iPhone 16 Pro 256G 原色钛金属 二手优品</v>
+      </c>
+      <c r="F66" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G66" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H66" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I66" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="67">
@@ -1536,13 +2332,25 @@
         <v>福建三明魏女</v>
       </c>
       <c r="C67" t="str">
-        <v>质检</v>
+        <v>1213332963</v>
       </c>
       <c r="D67" t="str">
-        <v>质检报告不认可</v>
+        <v>Q04CP7J7X1</v>
       </c>
       <c r="E67" t="str">
-        <v>已处理</v>
+        <v>平板电脑 苹果 iPad 9 (2021) 10.2英寸 64G 银色 二手优品</v>
+      </c>
+      <c r="F67" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G67" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H67" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I67" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="68">
@@ -1553,13 +2361,25 @@
         <v>山东-济南-董其泽</v>
       </c>
       <c r="C68" t="str">
-        <v>质检</v>
+        <v>1212607241</v>
       </c>
       <c r="D68" t="str">
-        <v>质检报告不认可</v>
+        <v>353878101895318</v>
       </c>
       <c r="E68" t="str">
-        <v>已处理</v>
+        <v>手机 7新 苹果 iPhone 11 Pro 256G 暗夜绿色 二手优品</v>
+      </c>
+      <c r="F68" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G68" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H68" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I68" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="69">
@@ -1570,13 +2390,25 @@
         <v>山东-菏泽-赵豪</v>
       </c>
       <c r="C69" t="str">
-        <v>质检</v>
+        <v>1211330450</v>
       </c>
       <c r="D69" t="str">
-        <v>质检报告不认可</v>
+        <v>T3N0CX04C69512A</v>
       </c>
       <c r="E69" t="str">
+        <v xml:space="preserve">笔记本 99新 华硕 华硕 无畏 Pro 14 2025 银色 </v>
+      </c>
+      <c r="F69" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G69" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H69" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I69" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="70">
@@ -1587,13 +2419,25 @@
         <v>浙江-杭州-杨广恩</v>
       </c>
       <c r="C70" t="str">
-        <v>质检</v>
+        <v>1211942181</v>
       </c>
       <c r="D70" t="str">
-        <v>质检报告不认可</v>
+        <v>869375055643411</v>
       </c>
       <c r="E70" t="str">
+        <v>手机 7新 vivo vivo iQOO Neo 5 活力版 8GB+256G 极夜黑 二手优品</v>
+      </c>
+      <c r="F70" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G70" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H70" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I70" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="71">
@@ -1604,13 +2448,25 @@
         <v>重庆-重庆-辜宏亮</v>
       </c>
       <c r="C71" t="str">
-        <v>质检</v>
+        <v>1213221429</v>
       </c>
       <c r="D71" t="str">
-        <v>质检报告不认可</v>
+        <v>867497076629740</v>
       </c>
       <c r="E71" t="str">
-        <v>已处理</v>
+        <v>华为 Mate 70 Pro</v>
+      </c>
+      <c r="F71" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G71" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H71" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I71" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="72">
@@ -1621,13 +2477,25 @@
         <v>山东-济南-薛亚伟</v>
       </c>
       <c r="C72" t="str">
-        <v>质检</v>
+        <v>1213266475</v>
       </c>
       <c r="D72" t="str">
-        <v>质检报告不认可</v>
+        <v>868479071354820</v>
       </c>
       <c r="E72" t="str">
+        <v>手机 99新 红米 红米 K80 至尊版 16GB+512G 砂岩灰 二手优品</v>
+      </c>
+      <c r="F72" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G72" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H72" t="str">
         <v>处理中</v>
+      </c>
+      <c r="I72" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="73">
@@ -1638,13 +2506,25 @@
         <v>江苏-南通-刘鑫</v>
       </c>
       <c r="C73" t="str">
-        <v>质检</v>
+        <v>1213190121</v>
       </c>
       <c r="D73" t="str">
-        <v>质检报告不认可</v>
+        <v>352224838201176</v>
       </c>
       <c r="E73" t="str">
+        <v>苹果 iPhone 17 Pro Max</v>
+      </c>
+      <c r="F73" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G73" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H73" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I73" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="74">
@@ -1655,13 +2535,25 @@
         <v>山西-太原-郑连珍</v>
       </c>
       <c r="C74" t="str">
-        <v>质检</v>
+        <v>1213225790</v>
       </c>
       <c r="D74" t="str">
-        <v>质检报告不认可</v>
+        <v>863815060583744</v>
       </c>
       <c r="E74" t="str">
+        <v>智能手表 7新以下 小天才 小天才 电话手表 Z8 1G+32G 碧海蓝 二手优品</v>
+      </c>
+      <c r="F74" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G74" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H74" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I74" t="str">
+        <v>智能手表</v>
       </c>
     </row>
     <row r="75">
@@ -1672,13 +2564,25 @@
         <v>江苏-淮安-夏前奇</v>
       </c>
       <c r="C75" t="str">
-        <v>质检</v>
+        <v>1213247462</v>
       </c>
       <c r="D75" t="str">
-        <v>质检报告不认可</v>
+        <v>356334108218952</v>
       </c>
       <c r="E75" t="str">
+        <v>苹果 iPhone 11</v>
+      </c>
+      <c r="F75" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G75" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H75" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I75" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="76">
@@ -1689,13 +2593,25 @@
         <v>江西-南昌-王诚</v>
       </c>
       <c r="C76" t="str">
-        <v>质检</v>
+        <v>1213120273</v>
       </c>
       <c r="D76" t="str">
-        <v>质检报告不认可</v>
+        <v>868479076223764</v>
       </c>
       <c r="E76" t="str">
+        <v>红米 K80 至尊版</v>
+      </c>
+      <c r="F76" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G76" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H76" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I76" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="77">
@@ -1706,13 +2622,25 @@
         <v>广东-广州-赵华武</v>
       </c>
       <c r="C77" t="str">
-        <v>质检</v>
+        <v>1212095258</v>
       </c>
       <c r="D77" t="str">
-        <v>质检报告不认可</v>
+        <v>861737084422752</v>
       </c>
       <c r="E77" t="str">
+        <v>OPPO Find X9</v>
+      </c>
+      <c r="F77" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G77" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H77" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I77" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="78">
@@ -1723,13 +2651,25 @@
         <v>辽宁-沈阳-李雪婷</v>
       </c>
       <c r="C78" t="str">
-        <v>质检</v>
+        <v>1213241926</v>
       </c>
       <c r="D78" t="str">
-        <v>质检报告不认可</v>
+        <v>KWH7VN214T</v>
       </c>
       <c r="E78" t="str">
-        <v>已处理</v>
+        <v>苹果 iPad Air8 13.0英寸 (M4) 2026</v>
+      </c>
+      <c r="F78" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G78" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H78" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I78" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="79">
@@ -1740,13 +2680,25 @@
         <v>江西-南昌-周凯</v>
       </c>
       <c r="C79" t="str">
-        <v>质检</v>
+        <v>1212976035</v>
       </c>
       <c r="D79" t="str">
-        <v>质检报告不认可</v>
+        <v>866478067140195</v>
       </c>
       <c r="E79" t="str">
+        <v>一加 Ace 2V</v>
+      </c>
+      <c r="F79" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G79" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H79" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I79" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="80">
@@ -1757,13 +2709,25 @@
         <v>李化学</v>
       </c>
       <c r="C80" t="str">
-        <v>质检</v>
+        <v>1213222881</v>
       </c>
       <c r="D80" t="str">
-        <v>质检报告不认可</v>
+        <v>865775043095513</v>
       </c>
       <c r="E80" t="str">
-        <v>已处理</v>
+        <v>小米 CC9 Pro</v>
+      </c>
+      <c r="F80" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G80" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H80" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I80" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="81">
@@ -1774,13 +2738,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C81" t="str">
-        <v>质检</v>
+        <v>1211557335</v>
       </c>
       <c r="D81" t="str">
-        <v>质检报告不认可</v>
+        <v>350432085103431</v>
       </c>
       <c r="E81" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 15 Pro</v>
+      </c>
+      <c r="F81" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G81" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H81" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I81" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="82">
@@ -1791,13 +2767,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C82" t="str">
-        <v>质检</v>
+        <v>1212940513</v>
       </c>
       <c r="D82" t="str">
-        <v>质检报告不认可</v>
+        <v>866103060651721</v>
       </c>
       <c r="E82" t="str">
+        <v>手机 7新 红米 红米 K50 至尊版 12GB+512G 银迹 二手优品</v>
+      </c>
+      <c r="F82" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G82" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H82" t="str">
         <v>处理中</v>
+      </c>
+      <c r="I82" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="83">
@@ -1808,13 +2796,25 @@
         <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C83" t="str">
-        <v>质检</v>
+        <v>1213152991</v>
       </c>
       <c r="D83" t="str">
-        <v>质检报告不认可</v>
+        <v>866528058674725</v>
       </c>
       <c r="E83" t="str">
+        <v>手机 7新 华为 华为 P50 Pro (麒麟版) 8GB+512G 雪域白 二手优品</v>
+      </c>
+      <c r="F83" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G83" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H83" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I83" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="84">
@@ -1825,13 +2825,25 @@
         <v>江西-南昌-袁志</v>
       </c>
       <c r="C84" t="str">
-        <v>质检</v>
+        <v>1213138855</v>
       </c>
       <c r="D84" t="str">
-        <v>质检报告不认可</v>
+        <v>863740086464986</v>
       </c>
       <c r="E84" t="str">
+        <v>红米 Turbo 4 Pro</v>
+      </c>
+      <c r="F84" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G84" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H84" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I84" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="85">
@@ -1842,13 +2854,25 @@
         <v>江苏-常州-陈涛</v>
       </c>
       <c r="C85" t="str">
-        <v>质检</v>
+        <v>1213226129</v>
       </c>
       <c r="D85" t="str">
-        <v>质检报告不认可</v>
+        <v>867181046447850</v>
       </c>
       <c r="E85" t="str">
+        <v>红米 Note 8 Pro</v>
+      </c>
+      <c r="F85" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G85" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H85" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I85" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="86">
@@ -1859,13 +2883,25 @@
         <v>李化学</v>
       </c>
       <c r="C86" t="str">
-        <v>质检</v>
+        <v>1213181070</v>
       </c>
       <c r="D86" t="str">
-        <v>质检报告不认可</v>
+        <v>864878054488501</v>
       </c>
       <c r="E86" t="str">
-        <v>已处理</v>
+        <v>荣耀 X20 SE</v>
+      </c>
+      <c r="F86" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G86" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H86" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I86" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="87">
@@ -1876,13 +2912,25 @@
         <v>浙江-绍兴-张磊</v>
       </c>
       <c r="C87" t="str">
-        <v>质检</v>
+        <v>1213151051</v>
       </c>
       <c r="D87" t="str">
-        <v>质检报告不认可</v>
+        <v>350605829118548</v>
       </c>
       <c r="E87" t="str">
+        <v>手机 7新 苹果 iPhone 14 256G 星光色 BS机</v>
+      </c>
+      <c r="F87" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G87" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H87" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I87" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="88">
@@ -1893,13 +2941,25 @@
         <v>山东-济宁-于鲁川</v>
       </c>
       <c r="C88" t="str">
-        <v>质检</v>
+        <v>1213151708</v>
       </c>
       <c r="D88" t="str">
-        <v>质检报告不认可</v>
+        <v>DMPCFDN7PTRK</v>
       </c>
       <c r="E88" t="str">
-        <v>已处理</v>
+        <v>苹果 iPad Pro (2020) 11.0英寸</v>
+      </c>
+      <c r="F88" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G88" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H88" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I88" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="89">
@@ -1910,13 +2970,25 @@
         <v>江苏-常州-陈涛</v>
       </c>
       <c r="C89" t="str">
-        <v>质检</v>
+        <v>1213226079</v>
       </c>
       <c r="D89" t="str">
-        <v>质检报告不认可</v>
+        <v>865363058071461</v>
       </c>
       <c r="E89" t="str">
+        <v>荣耀 X20</v>
+      </c>
+      <c r="F89" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G89" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H89" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I89" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="90">
@@ -1927,13 +2999,25 @@
         <v>江苏-常州-陈涛</v>
       </c>
       <c r="C90" t="str">
-        <v>质检</v>
+        <v>1213226137</v>
       </c>
       <c r="D90" t="str">
-        <v>质检报告不认可</v>
+        <v>864450085100123</v>
       </c>
       <c r="E90" t="str">
+        <v>红米 15R 5G</v>
+      </c>
+      <c r="F90" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G90" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H90" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I90" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="91">
@@ -1944,13 +3028,25 @@
         <v>丁凤腾</v>
       </c>
       <c r="C91" t="str">
-        <v>质检</v>
+        <v>1211380167</v>
       </c>
       <c r="D91" t="str">
-        <v>质检报告不认可</v>
+        <v>351111565692316</v>
       </c>
       <c r="E91" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 苹果 iPhone 14 Plus 256G 红色 BS机</v>
+      </c>
+      <c r="F91" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G91" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H91" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I91" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="92">
@@ -1961,13 +3057,25 @@
         <v>浙江-杭州-王华山</v>
       </c>
       <c r="C92" t="str">
-        <v>质检</v>
+        <v>1009319791</v>
       </c>
       <c r="D92" t="str">
-        <v>质检报告不认可</v>
+        <v>866214036015287</v>
       </c>
       <c r="E92" t="str">
+        <v>手机 95新 华为 华为 Mate 10 4GB+64G 亮黑色 二手优品</v>
+      </c>
+      <c r="F92" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G92" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H92" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I92" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="93">
@@ -1978,13 +3086,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C93" t="str">
-        <v>质检</v>
+        <v>1211001858</v>
       </c>
       <c r="D93" t="str">
-        <v>质检报告不认可</v>
+        <v>359065916823800</v>
       </c>
       <c r="E93" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 14 Pro</v>
+      </c>
+      <c r="F93" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G93" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H93" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I93" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="94">
@@ -1995,13 +3115,25 @@
         <v>广东-深圳-任迎超</v>
       </c>
       <c r="C94" t="str">
-        <v>质检</v>
+        <v>1005493055</v>
       </c>
       <c r="D94" t="str">
-        <v>质检报告不认可</v>
+        <v>356103509790061</v>
       </c>
       <c r="E94" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 苹果 iPhone 15 Pro Max 256G 蓝色钛金属 二手优品</v>
+      </c>
+      <c r="F94" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G94" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H94" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I94" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="95">
@@ -2012,13 +3144,25 @@
         <v>甘肃-天水-王娟</v>
       </c>
       <c r="C95" t="str">
-        <v>质检</v>
+        <v>1211555397</v>
       </c>
       <c r="D95" t="str">
-        <v>质检报告不认可</v>
+        <v>867413087298359</v>
       </c>
       <c r="E95" t="str">
+        <v>手机 99新 vivo vivo iQOO 15 16GB+512G 传奇版 二手优品</v>
+      </c>
+      <c r="F95" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G95" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H95" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I95" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="96">
@@ -2029,13 +3173,25 @@
         <v>山东-济南-房超</v>
       </c>
       <c r="C96" t="str">
-        <v>质检</v>
+        <v>1212431794</v>
       </c>
       <c r="D96" t="str">
-        <v>质检报告不认可</v>
+        <v>863553051225054</v>
       </c>
       <c r="E96" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 11 Ultra 12GB+256G 陶瓷黑 二手优品</v>
+      </c>
+      <c r="F96" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G96" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H96" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I96" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="97">
@@ -2046,13 +3202,25 @@
         <v>山东-济南-房超</v>
       </c>
       <c r="C97" t="str">
-        <v>质检</v>
+        <v>1213190093</v>
       </c>
       <c r="D97" t="str">
-        <v>质检报告不认可</v>
+        <v>352291519239577</v>
       </c>
       <c r="E97" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 13 Pro</v>
+      </c>
+      <c r="F97" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G97" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H97" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I97" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="98">
@@ -2063,13 +3231,25 @@
         <v>河北-邢台-付春静</v>
       </c>
       <c r="C98" t="str">
-        <v>质检</v>
+        <v>1007845663</v>
       </c>
       <c r="D98" t="str">
-        <v>质检报告不认可</v>
+        <v>869128072209413</v>
       </c>
       <c r="E98" t="str">
-        <v>已处理</v>
+        <v>手机 7新 vivo vivo S20 Pro 12GB+256G 紫气东来 二手优品</v>
+      </c>
+      <c r="F98" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G98" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H98" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I98" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="99">
@@ -2080,13 +3260,25 @@
         <v>浙江-杭州-郑培煌</v>
       </c>
       <c r="C99" t="str">
-        <v>质检</v>
+        <v>1211622542</v>
       </c>
       <c r="D99" t="str">
-        <v>质检报告不认可</v>
+        <v>862811079799232</v>
       </c>
       <c r="E99" t="str">
+        <v>手机 7新 vivo vivo iQOO 12 12GB+256G 传奇版 二手优品</v>
+      </c>
+      <c r="F99" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G99" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H99" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I99" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="100">
@@ -2097,13 +3289,25 @@
         <v>广东佛山孟吉祥</v>
       </c>
       <c r="C100" t="str">
-        <v>质检</v>
+        <v>1213008436</v>
       </c>
       <c r="D100" t="str">
-        <v>质检报告不认可</v>
+        <v>864226072897552</v>
       </c>
       <c r="E100" t="str">
-        <v>已处理</v>
+        <v>小米 15 Ultra</v>
+      </c>
+      <c r="F100" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G100" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H100" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I100" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="101">
@@ -2114,13 +3318,25 @@
         <v>江苏-南京-冯卯</v>
       </c>
       <c r="C101" t="str">
-        <v>质检</v>
+        <v>1213106623</v>
       </c>
       <c r="D101" t="str">
-        <v>质检报告不认可</v>
+        <v>PF3N32YF</v>
       </c>
       <c r="E101" t="str">
-        <v>已处理</v>
+        <v xml:space="preserve">笔记本 7新以下 联想 联想 拯救者 Y9000P 2022 钛晶灰 </v>
+      </c>
+      <c r="F101" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G101" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H101" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I101" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="102">
@@ -2131,13 +3347,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C102" t="str">
-        <v>质检</v>
+        <v>1212940373</v>
       </c>
       <c r="D102" t="str">
-        <v>质检报告不认可</v>
+        <v>861073060933780</v>
       </c>
       <c r="E102" t="str">
+        <v>手机 7新以下 小米 小米 MIX FOLD 2 12GB+512G 星耀金 二手优品</v>
+      </c>
+      <c r="F102" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G102" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H102" t="str">
         <v>处理中</v>
+      </c>
+      <c r="I102" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="103">
@@ -2148,13 +3376,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C103" t="str">
-        <v>质检</v>
+        <v>1212940531</v>
       </c>
       <c r="D103" t="str">
-        <v>质检报告不认可</v>
+        <v>865928063634162</v>
       </c>
       <c r="E103" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 12S 8GB+256G 白色 二手优品</v>
+      </c>
+      <c r="F103" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G103" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H103" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I103" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="104">
@@ -2165,13 +3405,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C104" t="str">
-        <v>质检</v>
+        <v>1212940514</v>
       </c>
       <c r="D104" t="str">
-        <v>质检报告不认可</v>
+        <v>867456075021200</v>
       </c>
       <c r="E104" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 14 Pro 16GB+512G 黑色 二手优品</v>
+      </c>
+      <c r="F104" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G104" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H104" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I104" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="105">
@@ -2182,13 +3434,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C105" t="str">
-        <v>质检</v>
+        <v>1212940395</v>
       </c>
       <c r="D105" t="str">
-        <v>质检报告不认可</v>
+        <v>865430074213839</v>
       </c>
       <c r="E105" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 MIX FOLD 4 16GB+512G 黑色 二手优品</v>
+      </c>
+      <c r="F105" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G105" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H105" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I105" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="106">
@@ -2199,13 +3463,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C106" t="str">
-        <v>质检</v>
+        <v>1212940491</v>
       </c>
       <c r="D106" t="str">
-        <v>质检报告不认可</v>
+        <v>865430070800860</v>
       </c>
       <c r="E106" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 MIX FOLD 4 16GB+512G 白色 二手优品</v>
+      </c>
+      <c r="F106" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G106" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H106" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I106" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="107">
@@ -2216,13 +3492,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C107" t="str">
-        <v>质检</v>
+        <v>1212940396</v>
       </c>
       <c r="D107" t="str">
-        <v>质检报告不认可</v>
+        <v>865430074602007</v>
       </c>
       <c r="E107" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 MIX FOLD 4 16GB+512G 白色 二手优品</v>
+      </c>
+      <c r="F107" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G107" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H107" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I107" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="108">
@@ -2233,13 +3521,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C108" t="str">
-        <v>质检</v>
+        <v>1212940424</v>
       </c>
       <c r="D108" t="str">
-        <v>质检报告不认可</v>
+        <v>867776076684361</v>
       </c>
       <c r="E108" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 15 Pro 16GB+1T 云杉绿 二手优品</v>
+      </c>
+      <c r="F108" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G108" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H108" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I108" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="109">
@@ -2250,13 +3550,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C109" t="str">
-        <v>质检</v>
+        <v>1212940479</v>
       </c>
       <c r="D109" t="str">
-        <v>质检报告不认可</v>
+        <v>864627074520177</v>
       </c>
       <c r="E109" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 15 Pro 16GB+512G 云杉绿 二手优品</v>
+      </c>
+      <c r="F109" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G109" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H109" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I109" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="110">
@@ -2267,13 +3579,25 @@
         <v>河南-郑州-黄倩</v>
       </c>
       <c r="C110" t="str">
-        <v>质检</v>
+        <v>1213022657</v>
       </c>
       <c r="D110" t="str">
-        <v>质检报告不认可</v>
+        <v>355536448982045</v>
       </c>
       <c r="E110" t="str">
+        <v>手机 7新以下 苹果 iPhone 14 256G 紫色 二手优品</v>
+      </c>
+      <c r="F110" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G110" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H110" t="str">
         <v>处理中</v>
+      </c>
+      <c r="I110" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="111">
@@ -2284,13 +3608,25 @@
         <v>云南-昆明-米丹</v>
       </c>
       <c r="C111" t="str">
-        <v>质检</v>
+        <v>1211393919</v>
       </c>
       <c r="D111" t="str">
-        <v>质检报告不认可</v>
+        <v>868501083160711</v>
       </c>
       <c r="E111" t="str">
-        <v>已处理</v>
+        <v>vivo iQOO Z10x</v>
+      </c>
+      <c r="F111" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G111" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H111" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I111" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="112">
@@ -2301,13 +3637,25 @@
         <v>安徽合肥王冬冬</v>
       </c>
       <c r="C112" t="str">
-        <v>质检</v>
+        <v>1213070989</v>
       </c>
       <c r="D112" t="str">
-        <v>质检报告不认可</v>
+        <v>861205073329735</v>
       </c>
       <c r="E112" t="str">
-        <v>已处理</v>
+        <v>手机 9新 vivo vivo iQOO Neo 10 16GB+512G 驰光白 二手优品</v>
+      </c>
+      <c r="F112" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G112" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H112" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I112" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="113">
@@ -2318,13 +3666,25 @@
         <v>安徽合肥王冬冬</v>
       </c>
       <c r="C113" t="str">
-        <v>质检</v>
+        <v>1213070988</v>
       </c>
       <c r="D113" t="str">
-        <v>质检报告不认可</v>
+        <v>863762057132418</v>
       </c>
       <c r="E113" t="str">
-        <v>已处理</v>
+        <v>手机 7新 华为 华为 Mate 40 Pro (4G) 8GB+256G 釉白色 二手优品</v>
+      </c>
+      <c r="F113" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G113" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H113" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I113" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="114">
@@ -2335,13 +3695,25 @@
         <v>李化学</v>
       </c>
       <c r="C114" t="str">
-        <v>质检</v>
+        <v>1213070421</v>
       </c>
       <c r="D114" t="str">
-        <v>质检报告不认可</v>
+        <v>869920044582178</v>
       </c>
       <c r="E114" t="str">
-        <v>已处理</v>
+        <v>红米 K30 (5G)</v>
+      </c>
+      <c r="F114" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G114" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H114" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I114" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="115">
@@ -2352,13 +3724,25 @@
         <v>广东-深圳-苏宇晖</v>
       </c>
       <c r="C115" t="str">
-        <v>质检</v>
+        <v>1211536920</v>
       </c>
       <c r="D115" t="str">
-        <v>质检报告不认可</v>
+        <v>X4WLHVG71T</v>
       </c>
       <c r="E115" t="str">
+        <v>智能手表 7新以下 苹果 Apple Watch Series 10 64G 亮黑色 官换机</v>
+      </c>
+      <c r="F115" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G115" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H115" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I115" t="str">
+        <v>智能手表</v>
       </c>
     </row>
     <row r="116">
@@ -2369,13 +3753,25 @@
         <v>江苏-南通-刘鑫</v>
       </c>
       <c r="C116" t="str">
-        <v>质检</v>
+        <v>1213002621</v>
       </c>
       <c r="D116" t="str">
-        <v>质检报告不认可</v>
+        <v>351072561782149</v>
       </c>
       <c r="E116" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 17 Pro Max</v>
+      </c>
+      <c r="F116" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G116" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H116" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I116" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="117">
@@ -2386,13 +3782,25 @@
         <v>江苏-南通-刘鑫</v>
       </c>
       <c r="C117" t="str">
-        <v>质检</v>
+        <v>1213002612</v>
       </c>
       <c r="D117" t="str">
-        <v>质检报告不认可</v>
+        <v>351072565263831</v>
       </c>
       <c r="E117" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 17 Pro Max</v>
+      </c>
+      <c r="F117" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G117" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H117" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I117" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="118">
@@ -2403,13 +3811,25 @@
         <v>江苏-淮安-张弛</v>
       </c>
       <c r="C118" t="str">
-        <v>质检</v>
+        <v>1213026632</v>
       </c>
       <c r="D118" t="str">
-        <v>质检报告不认可</v>
+        <v>860832077726474</v>
       </c>
       <c r="E118" t="str">
-        <v>已处理</v>
+        <v>华为 nova 14</v>
+      </c>
+      <c r="F118" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G118" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H118" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I118" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="119">
@@ -2420,13 +3840,25 @@
         <v>江苏-淮安-张弛</v>
       </c>
       <c r="C119" t="str">
-        <v>质检</v>
+        <v>1213026634</v>
       </c>
       <c r="D119" t="str">
-        <v>质检报告不认可</v>
+        <v>862442076782961</v>
       </c>
       <c r="E119" t="str">
-        <v>已处理</v>
+        <v>小米 15</v>
+      </c>
+      <c r="F119" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G119" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H119" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I119" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="120">
@@ -2437,13 +3869,25 @@
         <v>江苏-淮安-张弛</v>
       </c>
       <c r="C120" t="str">
-        <v>质检</v>
+        <v>1213026594</v>
       </c>
       <c r="D120" t="str">
-        <v>质检报告不认可</v>
+        <v>868587073306067</v>
       </c>
       <c r="E120" t="str">
-        <v>已处理</v>
+        <v>华为 nova 14</v>
+      </c>
+      <c r="F120" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G120" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H120" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I120" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="121">
@@ -2454,13 +3898,25 @@
         <v>江苏-淮安-张弛</v>
       </c>
       <c r="C121" t="str">
-        <v>质检</v>
+        <v>1213026633</v>
       </c>
       <c r="D121" t="str">
-        <v>质检报告不认可</v>
+        <v>869014073589187</v>
       </c>
       <c r="E121" t="str">
-        <v>已处理</v>
+        <v>小米 15</v>
+      </c>
+      <c r="F121" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G121" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H121" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I121" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="122">
@@ -2471,13 +3927,25 @@
         <v>广东-佛山-刘海滢</v>
       </c>
       <c r="C122" t="str">
-        <v>质检</v>
+        <v>1213014272</v>
       </c>
       <c r="D122" t="str">
-        <v>质检报告不认可</v>
+        <v>866132059560056</v>
       </c>
       <c r="E122" t="str">
-        <v>已处理</v>
+        <v>小米 Civi</v>
+      </c>
+      <c r="F122" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G122" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H122" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I122" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="123">
@@ -2488,13 +3956,25 @@
         <v>河南-郑州-黄倩</v>
       </c>
       <c r="C123" t="str">
-        <v>质检</v>
+        <v>1213022658</v>
       </c>
       <c r="D123" t="str">
-        <v>质检报告不认可</v>
+        <v>351156624102914</v>
       </c>
       <c r="E123" t="str">
+        <v>手机 7新以下 苹果 iPhone 13 Pro Max 128G 金色 二手优品</v>
+      </c>
+      <c r="F123" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G123" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H123" t="str">
         <v>处理中</v>
+      </c>
+      <c r="I123" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="124">
@@ -2505,13 +3985,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C124" t="str">
-        <v>质检</v>
+        <v>1212940444</v>
       </c>
       <c r="D124" t="str">
-        <v>质检报告不认可</v>
+        <v>864627073278090</v>
       </c>
       <c r="E124" t="str">
-        <v>已处理</v>
+        <v>手机 7新 小米 小米 15 Pro 16GB+512G 白色 二手优品</v>
+      </c>
+      <c r="F124" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G124" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H124" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I124" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="125">
@@ -2522,13 +4014,25 @@
         <v>广东佛山孟吉祥</v>
       </c>
       <c r="C125" t="str">
-        <v>质检</v>
+        <v>1213116423</v>
       </c>
       <c r="D125" t="str">
-        <v>质检报告不认可</v>
+        <v>861461082957327</v>
       </c>
       <c r="E125" t="str">
-        <v>已处理</v>
+        <v>红米 Note 15 Pro+</v>
+      </c>
+      <c r="F125" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G125" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H125" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I125" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="126">
@@ -2539,13 +4043,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C126" t="str">
-        <v>质检</v>
+        <v>1212914056</v>
       </c>
       <c r="D126" t="str">
-        <v>质检报告不认可</v>
+        <v>357313490626427</v>
       </c>
       <c r="E126" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 16 Pro Max</v>
+      </c>
+      <c r="F126" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G126" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H126" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I126" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="127">
@@ -2556,13 +4072,25 @@
         <v>云南-昆明-郎雄伟</v>
       </c>
       <c r="C127" t="str">
-        <v>质检</v>
+        <v>1212673156</v>
       </c>
       <c r="D127" t="str">
-        <v>质检报告不认可</v>
+        <v>867888072592017</v>
       </c>
       <c r="E127" t="str">
-        <v>已处理</v>
+        <v>realme GT7</v>
+      </c>
+      <c r="F127" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G127" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H127" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I127" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="128">
@@ -2573,13 +4101,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C128" t="str">
-        <v>质检</v>
+        <v>1212914051</v>
       </c>
       <c r="D128" t="str">
-        <v>质检报告不认可</v>
+        <v>865144074010745</v>
       </c>
       <c r="E128" t="str">
-        <v>已处理</v>
+        <v>华为 Pura 70</v>
+      </c>
+      <c r="F128" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G128" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H128" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I128" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="129">
@@ -2590,13 +4130,25 @@
         <v>广东-揭阳-杜晓彬</v>
       </c>
       <c r="C129" t="str">
-        <v>质检</v>
+        <v>1213017109</v>
       </c>
       <c r="D129" t="str">
-        <v>质检报告不认可</v>
+        <v>354325371030357</v>
       </c>
       <c r="E129" t="str">
-        <v>已处理</v>
+        <v>摩托罗拉 G100 Pro</v>
+      </c>
+      <c r="F129" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G129" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H129" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I129" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="130">
@@ -2607,13 +4159,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C130" t="str">
-        <v>质检</v>
+        <v>1212914059</v>
       </c>
       <c r="D130" t="str">
-        <v>质检报告不认可</v>
+        <v>5XQ0225430000842</v>
       </c>
       <c r="E130" t="str">
-        <v>已处理</v>
+        <v>华为 MateBook Pro</v>
+      </c>
+      <c r="F130" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G130" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H130" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I130" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="131">
@@ -2624,13 +4188,25 @@
         <v>安徽-芜湖-包飞</v>
       </c>
       <c r="C131" t="str">
-        <v>质检</v>
+        <v>1212996104</v>
       </c>
       <c r="D131" t="str">
-        <v>质检报告不认可</v>
+        <v>863546078175880</v>
       </c>
       <c r="E131" t="str">
-        <v>已处理</v>
+        <v>手机 95新 红米 红米 K80 12GB+512G 玄夜黑 二手优品</v>
+      </c>
+      <c r="F131" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G131" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H131" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I131" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="132">
@@ -2641,13 +4217,25 @@
         <v>湖南-长沙-罗明凯</v>
       </c>
       <c r="C132" t="str">
-        <v>质检</v>
+        <v>1212914870</v>
       </c>
       <c r="D132" t="str">
-        <v>质检报告不认可</v>
+        <v>351867220664350</v>
       </c>
       <c r="E132" t="str">
-        <v>已处理</v>
+        <v>手机 8新 苹果 iPhone SE (第三代) 128G 星光色 二手优品</v>
+      </c>
+      <c r="F132" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G132" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H132" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I132" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="133">
@@ -2658,13 +4246,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C133" t="str">
-        <v>质检</v>
+        <v>1212516331</v>
       </c>
       <c r="D133" t="str">
-        <v>质检报告不认可</v>
+        <v>862827076641201</v>
       </c>
       <c r="E133" t="str">
-        <v>已处理</v>
+        <v>手机 7新 小米 小米 MIX FLIP 2 12GB+256G 贝壳白 二手优品</v>
+      </c>
+      <c r="F133" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G133" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H133" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I133" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="134">
@@ -2675,13 +4275,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C134" t="str">
-        <v>质检</v>
+        <v>1212914063</v>
       </c>
       <c r="D134" t="str">
-        <v>质检报告不认可</v>
+        <v>867344072760378</v>
       </c>
       <c r="E134" t="str">
-        <v>已处理</v>
+        <v>荣耀 X70</v>
+      </c>
+      <c r="F134" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G134" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H134" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I134" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="135">
@@ -2692,13 +4304,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C135" t="str">
-        <v>质检</v>
+        <v>1212914062</v>
       </c>
       <c r="D135" t="str">
-        <v>质检报告不认可</v>
+        <v>865594070805706</v>
       </c>
       <c r="E135" t="str">
-        <v>已处理</v>
+        <v>华为 nova 14 Pro</v>
+      </c>
+      <c r="F135" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G135" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H135" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I135" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="136">
@@ -2709,13 +4333,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C136" t="str">
-        <v>质检</v>
+        <v>1212914075</v>
       </c>
       <c r="D136" t="str">
-        <v>质检报告不认可</v>
+        <v>864563073814800</v>
       </c>
       <c r="E136" t="str">
-        <v>已处理</v>
+        <v>小米 17 Pro</v>
+      </c>
+      <c r="F136" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G136" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H136" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I136" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="137">
@@ -2726,13 +4362,25 @@
         <v>江苏-无锡-刘雪伟</v>
       </c>
       <c r="C137" t="str">
-        <v>质检</v>
+        <v>1212995349</v>
       </c>
       <c r="D137" t="str">
-        <v>质检报告不认可</v>
+        <v>351881909343012</v>
       </c>
       <c r="E137" t="str">
+        <v>手机 7新以下 苹果 iPhone 15 Plus 512G 蓝色 二手优品</v>
+      </c>
+      <c r="F137" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G137" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H137" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I137" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="138">
@@ -2743,13 +4391,25 @@
         <v>湖北-武汉-李俊杰</v>
       </c>
       <c r="C138" t="str">
-        <v>质检</v>
+        <v>1212919455</v>
       </c>
       <c r="D138" t="str">
-        <v>质检报告不认可</v>
+        <v>355377267106816</v>
       </c>
       <c r="E138" t="str">
+        <v>手机 7新以下 苹果 iPhone 15 256G 蓝色 二手优品</v>
+      </c>
+      <c r="F138" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G138" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H138" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I138" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="139">
@@ -2760,13 +4420,25 @@
         <v>浙江-杭州-向东</v>
       </c>
       <c r="C139" t="str">
-        <v>质检</v>
+        <v>1212995100</v>
       </c>
       <c r="D139" t="str">
-        <v>质检报告不认可</v>
+        <v>861678071713805</v>
       </c>
       <c r="E139" t="str">
-        <v>已处理</v>
+        <v>红米 K70 至尊版</v>
+      </c>
+      <c r="F139" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G139" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H139" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I139" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="140">
@@ -2777,13 +4449,25 @@
         <v>山西-太原-郑连珍</v>
       </c>
       <c r="C140" t="str">
-        <v>质检</v>
+        <v>1212957800</v>
       </c>
       <c r="D140" t="str">
-        <v>质检报告不认可</v>
+        <v>867706060893397</v>
       </c>
       <c r="E140" t="str">
-        <v>已处理</v>
+        <v>智能手表 95新 小天才 小天才 电话手表 D3 4G 绯云红 二手优品</v>
+      </c>
+      <c r="F140" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G140" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H140" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I140" t="str">
+        <v>智能手表</v>
       </c>
     </row>
     <row r="141">
@@ -2794,13 +4478,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C141" t="str">
-        <v>质检</v>
+        <v>1212940470</v>
       </c>
       <c r="D141" t="str">
-        <v>质检报告不认可</v>
+        <v>865430072765897</v>
       </c>
       <c r="E141" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 MIX FOLD 4 16GB+512G 白色 二手优品</v>
+      </c>
+      <c r="F141" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G141" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H141" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I141" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="142">
@@ -2811,13 +4507,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C142" t="str">
-        <v>质检</v>
+        <v>1212940403</v>
       </c>
       <c r="D142" t="str">
-        <v>质检报告不认可</v>
+        <v>864396047493595</v>
       </c>
       <c r="E142" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 8 SE 6GB+128G 灰色 二手优品</v>
+      </c>
+      <c r="F142" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G142" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H142" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I142" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="143">
@@ -2828,13 +4536,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C143" t="str">
-        <v>质检</v>
+        <v>1212940415</v>
       </c>
       <c r="D143" t="str">
-        <v>质检报告不认可</v>
+        <v>866189060198300</v>
       </c>
       <c r="E143" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 红米 红米 Note 11 (5G) 6GB+128G 浅梦星河 二手优品</v>
+      </c>
+      <c r="F143" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G143" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H143" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I143" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="144">
@@ -2845,13 +4565,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C144" t="str">
-        <v>质检</v>
+        <v>1212940413</v>
       </c>
       <c r="D144" t="str">
-        <v>质检报告不认可</v>
+        <v>864446063532469</v>
       </c>
       <c r="E144" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 13 8GB+256G 旷野绿 二手优品</v>
+      </c>
+      <c r="F144" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G144" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H144" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I144" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="145">
@@ -2862,13 +4594,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C145" t="str">
-        <v>质检</v>
+        <v>1212940397</v>
       </c>
       <c r="D145" t="str">
-        <v>质检报告不认可</v>
+        <v>865276059649400</v>
       </c>
       <c r="E145" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 红米 红米 Note 9 Pro (5G) 8GB+256G 碧海星辰 二手优品</v>
+      </c>
+      <c r="F145" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G145" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H145" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I145" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="146">
@@ -2879,13 +4623,25 @@
         <v>安徽-合肥-张荣营</v>
       </c>
       <c r="C146" t="str">
-        <v>质检</v>
+        <v>1212943546</v>
       </c>
       <c r="D146" t="str">
-        <v>质检报告不认可</v>
+        <v>862542066746395</v>
       </c>
       <c r="E146" t="str">
-        <v>已处理</v>
+        <v>手机 7新 vivo vivo iQOO Neo 8 Pro 16GB+1T 冲浪 二手优品</v>
+      </c>
+      <c r="F146" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G146" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H146" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I146" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="147">
@@ -2896,13 +4652,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C147" t="str">
-        <v>质检</v>
+        <v>1212940455</v>
       </c>
       <c r="D147" t="str">
-        <v>质检报告不认可</v>
+        <v>866515056818149</v>
       </c>
       <c r="E147" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 红米 红米 Note 11 (5G) 8GB+256G 神秘黑境 二手优品</v>
+      </c>
+      <c r="F147" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G147" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H147" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I147" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="148">
@@ -2913,13 +4681,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C148" t="str">
-        <v>质检</v>
+        <v>1212940452</v>
       </c>
       <c r="D148" t="str">
-        <v>质检报告不认可</v>
+        <v>865430075793631</v>
       </c>
       <c r="E148" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 MIX FOLD 4 16GB+512G 白色 二手优品</v>
+      </c>
+      <c r="F148" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G148" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H148" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I148" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="149">
@@ -2930,13 +4710,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C149" t="str">
-        <v>质检</v>
+        <v>1212940433</v>
       </c>
       <c r="D149" t="str">
-        <v>质检报告不认可</v>
+        <v>861073060793622</v>
       </c>
       <c r="E149" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 MIX FOLD 2 12GB+512G 星耀金 二手优品</v>
+      </c>
+      <c r="F149" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G149" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H149" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I149" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="150">
@@ -2947,13 +4739,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C150" t="str">
-        <v>质检</v>
+        <v>1212953325</v>
       </c>
       <c r="D150" t="str">
-        <v>质检报告不认可</v>
+        <v>865855036169747</v>
       </c>
       <c r="E150" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 红米 红米 Note 4X (联发科) 4GB+64G 磨砂黑 二手优品</v>
+      </c>
+      <c r="F150" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G150" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H150" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I150" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="151">
@@ -2964,13 +4768,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C151" t="str">
-        <v>质检</v>
+        <v>1212940401</v>
       </c>
       <c r="D151" t="str">
-        <v>质检报告不认可</v>
+        <v>869335064898265</v>
       </c>
       <c r="E151" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 13 Ultra 16GB+1T 橄榄绿 二手优品</v>
+      </c>
+      <c r="F151" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G151" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H151" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I151" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="152">
@@ -2981,13 +4797,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C152" t="str">
-        <v>质检</v>
+        <v>1212940402</v>
       </c>
       <c r="D152" t="str">
-        <v>质检报告不认可</v>
+        <v>869013067405004</v>
       </c>
       <c r="E152" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 小米 小米 12S Ultra 12GB+256G 冷杉绿 二手优品</v>
+      </c>
+      <c r="F152" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G152" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H152" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I152" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="153">
@@ -2998,13 +4826,25 @@
         <v>江苏-南京-冯卯</v>
       </c>
       <c r="C153" t="str">
-        <v>质检</v>
+        <v>1212953659</v>
       </c>
       <c r="D153" t="str">
-        <v>质检报告不认可</v>
+        <v>NKV250RND1WK10004E05351</v>
       </c>
       <c r="E153" t="str">
-        <v>已处理</v>
+        <v xml:space="preserve">笔记本 7新以下 七彩虹 七彩虹 隐星 P15 2024 碳源灰 </v>
+      </c>
+      <c r="F153" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G153" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H153" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I153" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="154">
@@ -3015,13 +4855,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C154" t="str">
-        <v>质检</v>
+        <v>1212914072</v>
       </c>
       <c r="D154" t="str">
-        <v>质检报告不认可</v>
+        <v>860357064629911</v>
       </c>
       <c r="E154" t="str">
-        <v>已处理</v>
+        <v>OPPO Find N2 Flip</v>
+      </c>
+      <c r="F154" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G154" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H154" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I154" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="155">
@@ -3032,13 +4884,25 @@
         <v>辽宁-沈阳-王文超</v>
       </c>
       <c r="C155" t="str">
-        <v>质检</v>
+        <v>1212865817</v>
       </c>
       <c r="D155" t="str">
-        <v>质检报告不认可</v>
+        <v>355862230592101</v>
       </c>
       <c r="E155" t="str">
-        <v>已处理</v>
+        <v>手机 99新 三星 三星 Galaxy S24 Ultra 12GB+512G 钛羽黄 二手优品</v>
+      </c>
+      <c r="F155" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G155" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H155" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I155" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="156">
@@ -3049,13 +4913,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C156" t="str">
-        <v>质检</v>
+        <v>1212914045</v>
       </c>
       <c r="D156" t="str">
-        <v>质检报告不认可</v>
+        <v>GM61V700DF</v>
       </c>
       <c r="E156" t="str">
-        <v>已处理</v>
+        <v>苹果 Apple Watch Ultra 3</v>
+      </c>
+      <c r="F156" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G156" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H156" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I156" t="str">
+        <v>智能手表</v>
       </c>
     </row>
     <row r="157">
@@ -3066,13 +4942,25 @@
         <v>安徽-合肥-韦波</v>
       </c>
       <c r="C157" t="str">
-        <v>质检</v>
+        <v>1212867562</v>
       </c>
       <c r="D157" t="str">
-        <v>质检报告不认可</v>
+        <v>359394640535328</v>
       </c>
       <c r="E157" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 12 Pro</v>
+      </c>
+      <c r="F157" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G157" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H157" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I157" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="158">
@@ -3083,13 +4971,25 @@
         <v>重庆-徐若鸿</v>
       </c>
       <c r="C158" t="str">
-        <v>质检</v>
+        <v>1212951418</v>
       </c>
       <c r="D158" t="str">
-        <v>质检报告不认可</v>
+        <v>866014079661470</v>
       </c>
       <c r="E158" t="str">
-        <v>已处理</v>
+        <v>OPPO Find X8 Ultra 卫星通信版</v>
+      </c>
+      <c r="F158" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G158" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H158" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I158" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="159">
@@ -3100,13 +5000,25 @@
         <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C159" t="str">
-        <v>质检</v>
+        <v>1212847172</v>
       </c>
       <c r="D159" t="str">
-        <v>质检报告不认可</v>
+        <v>866499085345459</v>
       </c>
       <c r="E159" t="str">
-        <v>已处理</v>
+        <v>vivo iQOO Neo11</v>
+      </c>
+      <c r="F159" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G159" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H159" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I159" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="160">
@@ -3117,13 +5029,25 @@
         <v>辽宁-沈阳-王文超</v>
       </c>
       <c r="C160" t="str">
-        <v>质检</v>
+        <v>1212865821</v>
       </c>
       <c r="D160" t="str">
-        <v>质检报告不认可</v>
+        <v>862393047750829</v>
       </c>
       <c r="E160" t="str">
+        <v>手机 华为 华为 Mate 40 RS 保时捷设计 12GB+512G 陶瓷白 二手优品</v>
+      </c>
+      <c r="F160" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G160" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H160" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I160" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="161">
@@ -3134,13 +5058,25 @@
         <v>北京-北京-刘英琪</v>
       </c>
       <c r="C161" t="str">
-        <v>质检</v>
+        <v>1212872825</v>
       </c>
       <c r="D161" t="str">
-        <v>质检报告不认可</v>
+        <v>N293JJCYTG</v>
       </c>
       <c r="E161" t="str">
-        <v>已处理</v>
+        <v>苹果 22年 13寸 MacBook Air(M2)</v>
+      </c>
+      <c r="F161" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G161" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H161" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I161" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="162">
@@ -3151,13 +5087,25 @@
         <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C162" t="str">
-        <v>质检</v>
+        <v>1212847304</v>
       </c>
       <c r="D162" t="str">
-        <v>质检报告不认可</v>
+        <v>867586088808399</v>
       </c>
       <c r="E162" t="str">
-        <v>已处理</v>
+        <v>OPPO Reno15</v>
+      </c>
+      <c r="F162" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G162" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H162" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I162" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="163">
@@ -3168,13 +5116,25 @@
         <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C163" t="str">
-        <v>质检</v>
+        <v>1212847170</v>
       </c>
       <c r="D163" t="str">
-        <v>质检报告不认可</v>
+        <v>867485080376358</v>
       </c>
       <c r="E163" t="str">
-        <v>已处理</v>
+        <v>一加 Ace 6</v>
+      </c>
+      <c r="F163" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G163" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H163" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I163" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="164">
@@ -3185,13 +5145,25 @@
         <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C164" t="str">
-        <v>质检</v>
+        <v>1212697235</v>
       </c>
       <c r="D164" t="str">
-        <v>质检报告不认可</v>
+        <v>867098082397692</v>
       </c>
       <c r="E164" t="str">
-        <v>已处理</v>
+        <v>一加 Ace 6T</v>
+      </c>
+      <c r="F164" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G164" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H164" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I164" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="165">
@@ -3202,13 +5174,25 @@
         <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C165" t="str">
-        <v>质检</v>
+        <v>1212697237</v>
       </c>
       <c r="D165" t="str">
-        <v>质检报告不认可</v>
+        <v>869740086185270</v>
       </c>
       <c r="E165" t="str">
-        <v>已处理</v>
+        <v>一加 15T</v>
+      </c>
+      <c r="F165" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G165" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H165" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I165" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="166">
@@ -3219,13 +5203,25 @@
         <v>河北-邢台-付春静</v>
       </c>
       <c r="C166" t="str">
-        <v>质检</v>
+        <v>1210466514</v>
       </c>
       <c r="D166" t="str">
-        <v>质检报告不认可</v>
+        <v>866673077994421</v>
       </c>
       <c r="E166" t="str">
+        <v>手机 9新 小米 小米 15 12GB+512G 亮银版 二手优品</v>
+      </c>
+      <c r="F166" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G166" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H166" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I166" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="167">
@@ -3236,13 +5232,25 @@
         <v>河北-邢台-付春静</v>
       </c>
       <c r="C167" t="str">
-        <v>质检</v>
+        <v>1210465792</v>
       </c>
       <c r="D167" t="str">
-        <v>质检报告不认可</v>
+        <v>866810062858522</v>
       </c>
       <c r="E167" t="str">
+        <v>手机 99新 华为 华为 Mate X5 12GB+512G 羽砂白 二手优品</v>
+      </c>
+      <c r="F167" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G167" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H167" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I167" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="168">
@@ -3253,13 +5261,25 @@
         <v>重庆-重庆-廖青山</v>
       </c>
       <c r="C168" t="str">
-        <v>质检</v>
+        <v>1212797483</v>
       </c>
       <c r="D168" t="str">
-        <v>质检报告不认可</v>
+        <v>862699087073116</v>
       </c>
       <c r="E168" t="str">
-        <v>已处理</v>
+        <v>手机 8新 vivo vivo Y60 6GB+256G 曜石黑 二手优品</v>
+      </c>
+      <c r="F168" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G168" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H168" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I168" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="169">
@@ -3270,13 +5290,25 @@
         <v>甘肃-天水-牛田雨</v>
       </c>
       <c r="C169" t="str">
-        <v>质检</v>
+        <v>1212878556</v>
       </c>
       <c r="D169" t="str">
-        <v>质检报告不认可</v>
+        <v>JWWYQ1XQ7D</v>
       </c>
       <c r="E169" t="str">
-        <v>已处理</v>
+        <v>苹果 iPad Air7 (2025) 11.0英寸</v>
+      </c>
+      <c r="F169" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G169" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H169" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I169" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="170">
@@ -3287,13 +5319,25 @@
         <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C170" t="str">
-        <v>质检</v>
+        <v>1212688669</v>
       </c>
       <c r="D170" t="str">
-        <v>质检报告不认可</v>
+        <v>351764712692785</v>
       </c>
       <c r="E170" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 13 Pro Max</v>
+      </c>
+      <c r="F170" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G170" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H170" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I170" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="171">
@@ -3304,13 +5348,25 @@
         <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C171" t="str">
-        <v>质检</v>
+        <v>1212688664</v>
       </c>
       <c r="D171" t="str">
-        <v>质检报告不认可</v>
+        <v>351131126825650</v>
       </c>
       <c r="E171" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 14 Pro</v>
+      </c>
+      <c r="F171" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G171" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H171" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I171" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="172">
@@ -3321,13 +5377,25 @@
         <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C172" t="str">
-        <v>质检</v>
+        <v>1212845154</v>
       </c>
       <c r="D172" t="str">
-        <v>质检报告不认可</v>
+        <v>352672480444850</v>
       </c>
       <c r="E172" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 13 Pro Max</v>
+      </c>
+      <c r="F172" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G172" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H172" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I172" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="173">
@@ -3338,13 +5406,25 @@
         <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C173" t="str">
-        <v>质检</v>
+        <v>1212845158</v>
       </c>
       <c r="D173" t="str">
-        <v>质检报告不认可</v>
+        <v>352851130695406</v>
       </c>
       <c r="E173" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 13 Pro Max</v>
+      </c>
+      <c r="F173" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G173" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H173" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I173" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="174">
@@ -3355,13 +5435,25 @@
         <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C174" t="str">
-        <v>质检</v>
+        <v>1212847311</v>
       </c>
       <c r="D174" t="str">
-        <v>质检报告不认可</v>
+        <v>867098089227678</v>
       </c>
       <c r="E174" t="str">
-        <v>已处理</v>
+        <v>一加 Ace 6T</v>
+      </c>
+      <c r="F174" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G174" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H174" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I174" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="175">
@@ -3372,13 +5464,25 @@
         <v>福建-南平-葛荣彪</v>
       </c>
       <c r="C175" t="str">
-        <v>质检</v>
+        <v>1212847309</v>
       </c>
       <c r="D175" t="str">
-        <v>质检报告不认可</v>
+        <v>861737083664073</v>
       </c>
       <c r="E175" t="str">
-        <v>已处理</v>
+        <v>OPPO Find X9</v>
+      </c>
+      <c r="F175" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G175" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H175" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I175" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="176">
@@ -3389,13 +5493,25 @@
         <v>广东-深圳-张洲豪</v>
       </c>
       <c r="C176" t="str">
-        <v>质检</v>
+        <v>1212793860</v>
       </c>
       <c r="D176" t="str">
-        <v>质检报告不认可</v>
+        <v>866771072729394</v>
       </c>
       <c r="E176" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 vivo vivo iQOO Z10 Turbo Pro 16GB+512G 云海白 二手优品</v>
+      </c>
+      <c r="F176" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G176" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H176" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I176" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="177">
@@ -3406,13 +5522,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C177" t="str">
-        <v>质检</v>
+        <v>1212610934</v>
       </c>
       <c r="D177" t="str">
-        <v>质检报告不认可</v>
+        <v>JNHM9TV96H</v>
       </c>
       <c r="E177" t="str">
-        <v>已处理</v>
+        <v>苹果 Apple Watch Hermès Ultra 2</v>
+      </c>
+      <c r="F177" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G177" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H177" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I177" t="str">
+        <v>智能手表</v>
       </c>
     </row>
     <row r="178">
@@ -3423,13 +5551,25 @@
         <v>山东-济南-房超</v>
       </c>
       <c r="C178" t="str">
-        <v>质检</v>
+        <v>1212897289</v>
       </c>
       <c r="D178" t="str">
-        <v>质检报告不认可</v>
+        <v>864446064624703</v>
       </c>
       <c r="E178" t="str">
-        <v>已处理</v>
+        <v>小米 13</v>
+      </c>
+      <c r="F178" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G178" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H178" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I178" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="179">
@@ -3440,13 +5580,25 @@
         <v>四川-成都-王付强</v>
       </c>
       <c r="C179" t="str">
-        <v>质检</v>
+        <v>1212725411</v>
       </c>
       <c r="D179" t="str">
-        <v>质检报告不认可</v>
+        <v>MX13C56R23</v>
       </c>
       <c r="E179" t="str">
-        <v>已处理</v>
+        <v>苹果 23年 15寸 MacBook Air(M2)</v>
+      </c>
+      <c r="F179" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G179" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H179" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I179" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="180">
@@ -3457,13 +5609,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C180" t="str">
-        <v>质检</v>
+        <v>1212214987</v>
       </c>
       <c r="D180" t="str">
-        <v>质检报告不认可</v>
+        <v>863808072011515</v>
       </c>
       <c r="E180" t="str">
-        <v>已处理</v>
+        <v>手机 9新 荣耀 荣耀 Magic 8 16GB+512G 旭日金 二手优品</v>
+      </c>
+      <c r="F180" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G180" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H180" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I180" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="181">
@@ -3474,13 +5638,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C181" t="str">
-        <v>质检</v>
+        <v>1212214846</v>
       </c>
       <c r="D181" t="str">
-        <v>质检报告不认可</v>
+        <v>863854076332762</v>
       </c>
       <c r="E181" t="str">
-        <v>已处理</v>
+        <v>手机 7新 华为 华为 Mate 60 Pro 12GB+256G 雅丹黑 官翻机</v>
+      </c>
+      <c r="F181" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G181" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H181" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I181" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="182">
@@ -3491,13 +5667,25 @@
         <v>河南-郑州-黄倩</v>
       </c>
       <c r="C182" t="str">
-        <v>质检</v>
+        <v>1009720243</v>
       </c>
       <c r="D182" t="str">
-        <v>质检报告不认可</v>
+        <v>351156624102914</v>
       </c>
       <c r="E182" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 苹果 iPhone 13 Pro Max 128G 金色 二手优品</v>
+      </c>
+      <c r="F182" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G182" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H182" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I182" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="183">
@@ -3508,13 +5696,25 @@
         <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C183" t="str">
-        <v>质检</v>
+        <v>1211495367</v>
       </c>
       <c r="D183" t="str">
-        <v>质检报告不认可</v>
+        <v>351374186599993</v>
       </c>
       <c r="E183" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 苹果 iPhone 15 Plus 256G 黑色 二手优品</v>
+      </c>
+      <c r="F183" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G183" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H183" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I183" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="184">
@@ -3525,13 +5725,25 @@
         <v>江苏-南京-许国军</v>
       </c>
       <c r="C184" t="str">
-        <v>质检</v>
+        <v>1212749667</v>
       </c>
       <c r="D184" t="str">
-        <v>质检报告不认可</v>
+        <v>352507503836700</v>
       </c>
       <c r="E184" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 13 Pro</v>
+      </c>
+      <c r="F184" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G184" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H184" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I184" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="185">
@@ -3542,13 +5754,25 @@
         <v>江苏-无锡-何炳爱</v>
       </c>
       <c r="C185" t="str">
-        <v>质检</v>
+        <v>1211433482</v>
       </c>
       <c r="D185" t="str">
-        <v>质检报告不认可</v>
+        <v>352784989008290</v>
       </c>
       <c r="E185" t="str">
-        <v>已处理</v>
+        <v>手机 9新 苹果 iPhone 14 Pro Max 512G 深空黑 二手优品</v>
+      </c>
+      <c r="F185" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G185" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H185" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I185" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="186">
@@ -3559,13 +5783,25 @@
         <v>四川-成都-程安材</v>
       </c>
       <c r="C186" t="str">
+        <v>1006302344</v>
+      </c>
+      <c r="D186" t="str">
+        <v>159402201624</v>
+      </c>
+      <c r="E186" t="str">
+        <v>95新 佳能 佳能 EOS R50 V 套机 黑色 undefined</v>
+      </c>
+      <c r="F186" t="str">
         <v>售后</v>
       </c>
-      <c r="D186" t="str">
+      <c r="G186" t="str">
         <v>售后退回有机损</v>
       </c>
-      <c r="E186" t="str">
+      <c r="H186" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I186" t="str">
+        <v/>
       </c>
     </row>
     <row r="187">
@@ -3576,13 +5812,25 @@
         <v>四川-成都-王付强</v>
       </c>
       <c r="C187" t="str">
-        <v>质检</v>
+        <v>1212792648</v>
       </c>
       <c r="D187" t="str">
-        <v>质检报告不认可</v>
+        <v>LGX1F09RL9</v>
       </c>
       <c r="E187" t="str">
-        <v>已处理</v>
+        <v xml:space="preserve">笔记本 95新 苹果 苹果 26年 13寸 MacBook Neo 柑橘黄色 </v>
+      </c>
+      <c r="F187" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G187" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H187" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I187" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="188">
@@ -3593,13 +5841,25 @@
         <v>安徽-亳州-陆盼盼</v>
       </c>
       <c r="C188" t="str">
-        <v>质检</v>
+        <v>1212692838</v>
       </c>
       <c r="D188" t="str">
-        <v>质检报告不认可</v>
+        <v>862234041892599</v>
       </c>
       <c r="E188" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 OPPO OPPO K7 8GB+128G 海夜 二手优品</v>
+      </c>
+      <c r="F188" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G188" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H188" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I188" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="189">
@@ -3610,13 +5870,25 @@
         <v>安徽-亳州-陆盼盼</v>
       </c>
       <c r="C189" t="str">
-        <v>质检</v>
+        <v>1212692846</v>
       </c>
       <c r="D189" t="str">
-        <v>质检报告不认可</v>
+        <v>863145056295156</v>
       </c>
       <c r="E189" t="str">
-        <v>已处理</v>
+        <v>手机 8新 OPPO OPPO Reno5 Pro 12GB+256G 极光蓝 二手优品</v>
+      </c>
+      <c r="F189" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G189" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H189" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I189" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="190">
@@ -3627,13 +5899,25 @@
         <v>河南-郑州-季森森</v>
       </c>
       <c r="C190" t="str">
-        <v>质检</v>
+        <v>1212674486</v>
       </c>
       <c r="D190" t="str">
-        <v>质检报告不认可</v>
+        <v>863229076186080</v>
       </c>
       <c r="E190" t="str">
-        <v>已处理</v>
+        <v>小米 15 Pro</v>
+      </c>
+      <c r="F190" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G190" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H190" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I190" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="191">
@@ -3644,13 +5928,25 @@
         <v>河南-郑州-季森森</v>
       </c>
       <c r="C191" t="str">
-        <v>质检</v>
+        <v>1212674484</v>
       </c>
       <c r="D191" t="str">
-        <v>质检报告不认可</v>
+        <v>862442073757966</v>
       </c>
       <c r="E191" t="str">
-        <v>已处理</v>
+        <v>小米 15</v>
+      </c>
+      <c r="F191" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G191" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H191" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I191" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="192">
@@ -3661,13 +5957,25 @@
         <v>福建-福州-王忠明</v>
       </c>
       <c r="C192" t="str">
-        <v>质检</v>
+        <v>1212720064</v>
       </c>
       <c r="D192" t="str">
-        <v>质检报告不认可</v>
+        <v>5GZBB25827200103</v>
       </c>
       <c r="E192" t="str">
+        <v>平板电脑 7新以下 华为 华为 MatePad Air 柔光版（2025）12.0英寸 12GB+256G 羽砂白 二手优品</v>
+      </c>
+      <c r="F192" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G192" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H192" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I192" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="193">
@@ -3678,13 +5986,25 @@
         <v>辽宁-沈阳-王海青</v>
       </c>
       <c r="C193" t="str">
-        <v>质检</v>
+        <v>1212474193</v>
       </c>
       <c r="D193" t="str">
-        <v>质检报告不认可</v>
+        <v>867311086193417</v>
       </c>
       <c r="E193" t="str">
-        <v>已处理</v>
+        <v>手机 7新 OPPO OPPO Reno15 16GB+512G 极光蓝 二手优品</v>
+      </c>
+      <c r="F193" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G193" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H193" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I193" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="194">
@@ -3695,13 +6015,25 @@
         <v>江苏-苏州-黄迪孟</v>
       </c>
       <c r="C194" t="str">
-        <v>质检</v>
+        <v>1212572470</v>
       </c>
       <c r="D194" t="str">
-        <v>质检报告不认可</v>
+        <v>865297076247978</v>
       </c>
       <c r="E194" t="str">
-        <v>已处理</v>
+        <v>OPPO Reno14</v>
+      </c>
+      <c r="F194" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G194" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H194" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I194" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="195">
@@ -3712,13 +6044,25 @@
         <v>山东-济南-戴志鹏</v>
       </c>
       <c r="C195" t="str">
-        <v>质检</v>
+        <v>1212728701</v>
       </c>
       <c r="D195" t="str">
-        <v>质检报告不认可</v>
+        <v>861289076615944</v>
       </c>
       <c r="E195" t="str">
-        <v>已处理</v>
+        <v>红米 K80</v>
+      </c>
+      <c r="F195" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G195" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H195" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I195" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="196">
@@ -3729,13 +6073,25 @@
         <v>湖北-武汉-黄武</v>
       </c>
       <c r="C196" t="str">
-        <v>质检</v>
+        <v>1211839366</v>
       </c>
       <c r="D196" t="str">
-        <v>质检报告不认可</v>
+        <v>9S90063</v>
       </c>
       <c r="E196" t="str">
+        <v xml:space="preserve">笔记本 9新 外星人 Alienware M15 R3 白色 </v>
+      </c>
+      <c r="F196" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G196" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H196" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I196" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="197">
@@ -3746,13 +6102,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C197" t="str">
-        <v>质检</v>
+        <v>1212750291</v>
       </c>
       <c r="D197" t="str">
-        <v>质检报告不认可</v>
+        <v>72HXYD3</v>
       </c>
       <c r="E197" t="str">
-        <v>已处理</v>
+        <v>外星人 Alienware X17 R1</v>
+      </c>
+      <c r="F197" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G197" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H197" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I197" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="198">
@@ -3763,13 +6131,25 @@
         <v>江苏-苏州-杨鲁攀</v>
       </c>
       <c r="C198" t="str">
-        <v>质检</v>
+        <v>1212542123</v>
       </c>
       <c r="D198" t="str">
-        <v>质检报告不认可</v>
+        <v>353879237713391</v>
       </c>
       <c r="E198" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone 13 Pro</v>
+      </c>
+      <c r="F198" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G198" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H198" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I198" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="199">
@@ -3780,13 +6160,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C199" t="str">
-        <v>质检</v>
+        <v>1212516327</v>
       </c>
       <c r="D199" t="str">
-        <v>质检报告不认可</v>
+        <v>353727580455898</v>
       </c>
       <c r="E199" t="str">
+        <v>手机 9新 三星 三星 Galaxy Z Flip7 12GB+256G 秘影黑 二手优品</v>
+      </c>
+      <c r="F199" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G199" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H199" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I199" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="200">
@@ -3797,13 +6189,25 @@
         <v>河南-郑州-焦威建</v>
       </c>
       <c r="C200" t="str">
-        <v>质检</v>
+        <v>1211503670</v>
       </c>
       <c r="D200" t="str">
-        <v>质检报告不认可</v>
+        <v>354770699854311</v>
       </c>
       <c r="E200" t="str">
-        <v>已处理</v>
+        <v>手机 95新 苹果 iPhone 13 Pro 256G 石墨色 二手优品</v>
+      </c>
+      <c r="F200" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G200" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H200" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I200" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="201">
@@ -3814,13 +6218,25 @@
         <v>广东-深圳-陈敬丽</v>
       </c>
       <c r="C201" t="str">
-        <v>质检</v>
+        <v>1212427043</v>
       </c>
       <c r="D201" t="str">
-        <v>质检报告不认可</v>
+        <v>863395046621306</v>
       </c>
       <c r="E201" t="str">
-        <v>已处理</v>
+        <v>手机 8新 红米 红米 10X (4G) 4GB+128G 冰雾白 二手优品</v>
+      </c>
+      <c r="F201" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G201" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H201" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I201" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="202">
@@ -3831,13 +6247,25 @@
         <v>安徽-阜阳-赵子军</v>
       </c>
       <c r="C202" t="str">
-        <v>质检</v>
+        <v>1212689863</v>
       </c>
       <c r="D202" t="str">
-        <v>质检报告不认可</v>
+        <v>864545072153017</v>
       </c>
       <c r="E202" t="str">
+        <v>手机 95新 荣耀 荣耀 Magic Vs3 12GB+512G 苔原绿 二手优品</v>
+      </c>
+      <c r="F202" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G202" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H202" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I202" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="203">
@@ -3848,13 +6276,25 @@
         <v>广东-深圳-迟恭彦</v>
       </c>
       <c r="C203" t="str">
-        <v>质检</v>
+        <v>1008509657</v>
       </c>
       <c r="D203" t="str">
-        <v>质检报告不认可</v>
+        <v>356719087217241</v>
       </c>
       <c r="E203" t="str">
-        <v>已处理</v>
+        <v>苹果 iPhone X</v>
+      </c>
+      <c r="F203" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G203" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H203" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I203" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="204">
@@ -3865,13 +6305,25 @@
         <v>河北-石家庄-赵飞</v>
       </c>
       <c r="C204" t="str">
-        <v>质检</v>
+        <v>1212662886</v>
       </c>
       <c r="D204" t="str">
-        <v>质检报告不认可</v>
+        <v>866854081064472</v>
       </c>
       <c r="E204" t="str">
-        <v>已处理</v>
+        <v>vivo X300</v>
+      </c>
+      <c r="F204" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G204" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H204" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I204" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="205">
@@ -3882,13 +6334,25 @@
         <v>浙江-杭州-涂婷婷</v>
       </c>
       <c r="C205" t="str">
-        <v>质检</v>
+        <v>1212571801</v>
       </c>
       <c r="D205" t="str">
-        <v>质检报告不认可</v>
+        <v>868575060980317</v>
       </c>
       <c r="E205" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 OPPO OPPO A2 Pro 12GB+512G 大漠棕 二手优品</v>
+      </c>
+      <c r="F205" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G205" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H205" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I205" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="206">
@@ -3899,13 +6363,25 @@
         <v>四川-成都-程安材</v>
       </c>
       <c r="C206" t="str">
-        <v>质检</v>
+        <v>1006302344</v>
       </c>
       <c r="D206" t="str">
-        <v>质检报告不认可</v>
+        <v>159402201624</v>
       </c>
       <c r="E206" t="str">
-        <v>已处理</v>
+        <v>佳能 EOS R50 V 套机</v>
+      </c>
+      <c r="F206" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G206" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H206" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I206" t="str">
+        <v>单电/微单套机</v>
       </c>
     </row>
     <row r="207">
@@ -3916,13 +6392,25 @@
         <v>江苏南京孙杰</v>
       </c>
       <c r="C207" t="str">
-        <v>质检</v>
+        <v>1212563835</v>
       </c>
       <c r="D207" t="str">
-        <v>质检报告不认可</v>
+        <v>5JB0223906000630</v>
       </c>
       <c r="E207" t="str">
-        <v>已处理</v>
+        <v>平板电脑 8新 华为 华为 MatePad Pro (2023) 13.2英寸 12GB+256G 曜金黑 展示机</v>
+      </c>
+      <c r="F207" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G207" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H207" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I207" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="208">
@@ -3933,13 +6421,25 @@
         <v>江苏-南京-王玉</v>
       </c>
       <c r="C208" t="str">
-        <v>质检</v>
+        <v>1009554030</v>
       </c>
       <c r="D208" t="str">
-        <v>质检报告不认可</v>
+        <v>359877775600917</v>
       </c>
       <c r="E208" t="str">
+        <v>手机 7新 苹果 iPhone 17 Pro 256G 银色 二手优品</v>
+      </c>
+      <c r="F208" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G208" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H208" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I208" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="209">
@@ -3950,13 +6450,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C209" t="str">
-        <v>质检</v>
+        <v>1212516326</v>
       </c>
       <c r="D209" t="str">
-        <v>质检报告不认可</v>
+        <v>862827071912649</v>
       </c>
       <c r="E209" t="str">
+        <v>手机 7新 小米 小米 MIX FLIP 2 12GB+512G 星云紫 二手优品</v>
+      </c>
+      <c r="F209" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G209" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H209" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I209" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="210">
@@ -3967,13 +6479,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C210" t="str">
-        <v>质检</v>
+        <v>1212516328</v>
       </c>
       <c r="D210" t="str">
-        <v>质检报告不认可</v>
+        <v>862827077324369</v>
       </c>
       <c r="E210" t="str">
+        <v>手机 8新 小米 小米 MIX FLIP 2 12GB+256G 贝壳白 二手优品</v>
+      </c>
+      <c r="F210" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G210" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H210" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I210" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="211">
@@ -3984,13 +6508,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C211" t="str">
-        <v>质检</v>
+        <v>1212516339</v>
       </c>
       <c r="D211" t="str">
-        <v>质检报告不认可</v>
+        <v>861263078887652</v>
       </c>
       <c r="E211" t="str">
+        <v>手机 8新 realme realme GT7 Pro 16GB+512G 光域白 二手优品</v>
+      </c>
+      <c r="F211" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G211" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H211" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I211" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="212">
@@ -4001,13 +6537,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C212" t="str">
-        <v>质检</v>
+        <v>1212516333</v>
       </c>
       <c r="D212" t="str">
-        <v>质检报告不认可</v>
+        <v>860942078623685</v>
       </c>
       <c r="E212" t="str">
+        <v>手机 9新 红米 红米 Note 15 Pro 12GB+512G 天青蓝 二手优品</v>
+      </c>
+      <c r="F212" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G212" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H212" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I212" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="213">
@@ -4018,13 +6566,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C213" t="str">
-        <v>质检</v>
+        <v>1212516330</v>
       </c>
       <c r="D213" t="str">
-        <v>质检报告不认可</v>
+        <v>863106086172963</v>
       </c>
       <c r="E213" t="str">
+        <v>手机 99新 荣耀 荣耀 400 12GB+512G 幻夜黑 二手优品</v>
+      </c>
+      <c r="F213" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G213" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H213" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I213" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="214">
@@ -4035,13 +6595,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C214" t="str">
-        <v>质检</v>
+        <v>1212516309</v>
       </c>
       <c r="D214" t="str">
-        <v>质检报告不认可</v>
+        <v>867084067043402</v>
       </c>
       <c r="E214" t="str">
+        <v>手机 7新 荣耀 荣耀 Magic 6 16GB+256G 绒黑色 二手优品</v>
+      </c>
+      <c r="F214" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G214" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H214" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I214" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="215">
@@ -4052,13 +6624,25 @@
         <v>湖北-武汉-何勇杰</v>
       </c>
       <c r="C215" t="str">
-        <v>质检</v>
+        <v>1212485039</v>
       </c>
       <c r="D215" t="str">
-        <v>质检报告不认可</v>
+        <v>864278080472738</v>
       </c>
       <c r="E215" t="str">
-        <v>已处理</v>
+        <v>vivo iQOO Z10 Turbo+</v>
+      </c>
+      <c r="F215" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G215" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H215" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I215" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="216">
@@ -4069,13 +6653,25 @@
         <v>李化学</v>
       </c>
       <c r="C216" t="str">
-        <v>质检</v>
+        <v>1212617330</v>
       </c>
       <c r="D216" t="str">
-        <v>质检报告不认可</v>
+        <v>862744046677373</v>
       </c>
       <c r="E216" t="str">
-        <v>已处理</v>
+        <v>手机 8新 vivo vivo Y70s 8GB+128G 星光蓝 二手优品</v>
+      </c>
+      <c r="F216" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G216" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H216" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I216" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="217">
@@ -4086,13 +6682,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C217" t="str">
-        <v>质检</v>
+        <v>1212610950</v>
       </c>
       <c r="D217" t="str">
-        <v>质检报告不认可</v>
+        <v>868023063023595</v>
       </c>
       <c r="E217" t="str">
-        <v>已处理</v>
+        <v>OPPO Reno10</v>
+      </c>
+      <c r="F217" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G217" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H217" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I217" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="218">
@@ -4103,13 +6711,25 @@
         <v>江苏盐城周婷婷</v>
       </c>
       <c r="C218" t="str">
-        <v>质检</v>
+        <v>1212603860</v>
       </c>
       <c r="D218" t="str">
-        <v>质检报告不认可</v>
+        <v>FT79WYP07D</v>
       </c>
       <c r="E218" t="str">
-        <v>已处理</v>
+        <v>苹果 iPad 11 (2025) 11.0英寸</v>
+      </c>
+      <c r="F218" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G218" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H218" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I218" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="219">
@@ -4120,13 +6740,25 @@
         <v>江苏盐城周婷婷</v>
       </c>
       <c r="C219" t="str">
-        <v>质检</v>
+        <v>1212603864</v>
       </c>
       <c r="D219" t="str">
-        <v>质检报告不认可</v>
+        <v>LWQ04X29F0</v>
       </c>
       <c r="E219" t="str">
-        <v>已处理</v>
+        <v>苹果 iPad Air8 11.0英寸 (M4) 2026</v>
+      </c>
+      <c r="F219" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G219" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H219" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I219" t="str">
+        <v>平板电脑</v>
       </c>
     </row>
     <row r="220">
@@ -4137,13 +6769,25 @@
         <v>陕西-西安-邵操操</v>
       </c>
       <c r="C220" t="str">
-        <v>质检</v>
+        <v>1212476858</v>
       </c>
       <c r="D220" t="str">
-        <v>质检报告不认可</v>
+        <v>865509078807272</v>
       </c>
       <c r="E220" t="str">
+        <v>手机 99新 vivo vivo X Fold 5 16GB+512G 钛度 二手优品</v>
+      </c>
+      <c r="F220" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G220" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H220" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I220" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="221">
@@ -4154,13 +6798,25 @@
         <v>陕西-西安-邵操操</v>
       </c>
       <c r="C221" t="str">
-        <v>质检</v>
+        <v>1212476857</v>
       </c>
       <c r="D221" t="str">
-        <v>质检报告不认可</v>
+        <v>865509077903015</v>
       </c>
       <c r="E221" t="str">
+        <v>手机 99新 vivo vivo X Fold 5 16GB+512G 青松 二手优品</v>
+      </c>
+      <c r="F221" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G221" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H221" t="str">
         <v>待处理</v>
+      </c>
+      <c r="I221" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="222">
@@ -4171,13 +6827,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C222" t="str">
-        <v>质检</v>
+        <v>1212620253</v>
       </c>
       <c r="D222" t="str">
-        <v>质检报告不认可</v>
+        <v>PF53275D</v>
       </c>
       <c r="E222" t="str">
-        <v>已处理</v>
+        <v>联想 拯救者 Y9000P 2024</v>
+      </c>
+      <c r="F222" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G222" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H222" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I222" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="223">
@@ -4188,13 +6856,25 @@
         <v>江苏-南京-邢希鸣</v>
       </c>
       <c r="C223" t="str">
-        <v>质检</v>
+        <v>1212620254</v>
       </c>
       <c r="D223" t="str">
-        <v>质检报告不认可</v>
+        <v>PF5EMKVM</v>
       </c>
       <c r="E223" t="str">
-        <v>已处理</v>
+        <v>联想 拯救者 R9000P 2024</v>
+      </c>
+      <c r="F223" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G223" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H223" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I223" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="224">
@@ -4205,13 +6885,25 @@
         <v>山西-太原-郑连珍</v>
       </c>
       <c r="C224" t="str">
-        <v>质检</v>
+        <v>1212475953</v>
       </c>
       <c r="D224" t="str">
-        <v>质检报告不认可</v>
+        <v>863187063412093</v>
       </c>
       <c r="E224" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 OPPO OPPO Find N3 12GB+512G 潜航黑 二手优品</v>
+      </c>
+      <c r="F224" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G224" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H224" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I224" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="225">
@@ -4222,13 +6914,25 @@
         <v>安徽-合肥-黄子龙</v>
       </c>
       <c r="C225" t="str">
-        <v>质检</v>
+        <v>1212568437</v>
       </c>
       <c r="D225" t="str">
-        <v>质检报告不认可</v>
+        <v>354603280211833</v>
       </c>
       <c r="E225" t="str">
-        <v>已处理</v>
+        <v>手机 95新 苹果 iPhone 16 Pro 256G 原色钛金属 二手优品</v>
+      </c>
+      <c r="F225" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G225" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H225" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I225" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="226">
@@ -4239,13 +6943,25 @@
         <v>安徽-合肥-彭鹏</v>
       </c>
       <c r="C226" t="str">
-        <v>质检</v>
+        <v>1212472124</v>
       </c>
       <c r="D226" t="str">
-        <v>质检报告不认可</v>
+        <v>PF3XXT1A</v>
       </c>
       <c r="E226" t="str">
+        <v xml:space="preserve">笔记本 7新以下 联想 联想 拯救者 Y7000P 2022 银色 </v>
+      </c>
+      <c r="F226" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G226" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H226" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I226" t="str">
+        <v>笔记本</v>
       </c>
     </row>
     <row r="227">
@@ -4256,13 +6972,25 @@
         <v>李化学</v>
       </c>
       <c r="C227" t="str">
-        <v>质检</v>
+        <v>1212555298</v>
       </c>
       <c r="D227" t="str">
-        <v>质检报告不认可</v>
+        <v>860386071290326</v>
       </c>
       <c r="E227" t="str">
-        <v>已处理</v>
+        <v>手机 8新 荣耀 荣耀 X50i+ 12GB+256G 云水蓝 二手优品</v>
+      </c>
+      <c r="F227" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G227" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H227" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I227" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="228">
@@ -4273,13 +7001,25 @@
         <v>河南-郑州-王淑豪</v>
       </c>
       <c r="C228" t="str">
-        <v>质检</v>
+        <v>1212397892</v>
       </c>
       <c r="D228" t="str">
-        <v>质检报告不认可</v>
+        <v>863416080656303</v>
       </c>
       <c r="E228" t="str">
-        <v>已处理</v>
+        <v>手机 95新 荣耀 荣耀 600 Pro 16GB+512G 曜石黑 二手优品</v>
+      </c>
+      <c r="F228" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G228" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H228" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I228" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="229">
@@ -4290,13 +7030,25 @@
         <v>江西-南昌-胡华波</v>
       </c>
       <c r="C229" t="str">
-        <v>质检</v>
+        <v>1212497601</v>
       </c>
       <c r="D229" t="str">
-        <v>质检报告不认可</v>
+        <v>863908083992966</v>
       </c>
       <c r="E229" t="str">
-        <v>已处理</v>
+        <v>红米 K90 Pro Max</v>
+      </c>
+      <c r="F229" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G229" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H229" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I229" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="230">
@@ -4307,13 +7059,25 @@
         <v>李志远</v>
       </c>
       <c r="C230" t="str">
-        <v>质检</v>
+        <v>1212506897</v>
       </c>
       <c r="D230" t="str">
-        <v>质检报告不认可</v>
+        <v>861186082707667</v>
       </c>
       <c r="E230" t="str">
-        <v>已处理</v>
+        <v>华为 畅享 70X 尊享版</v>
+      </c>
+      <c r="F230" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G230" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H230" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I230" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="231">
@@ -4324,13 +7088,25 @@
         <v>辽宁-沈阳-刘海旭</v>
       </c>
       <c r="C231" t="str">
-        <v>质检</v>
+        <v>1211041923</v>
       </c>
       <c r="D231" t="str">
-        <v>质检报告不认可</v>
+        <v>862472078727383</v>
       </c>
       <c r="E231" t="str">
+        <v>手机 7新以下 华为 华为 nova 13 12GB+512G 羽砂白 二手优品</v>
+      </c>
+      <c r="F231" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G231" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H231" t="str">
         <v>处理中</v>
+      </c>
+      <c r="I231" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="232">
@@ -4341,13 +7117,25 @@
         <v>广东-深圳-侯晓鹏</v>
       </c>
       <c r="C232" t="str">
-        <v>质检</v>
+        <v>1212516332</v>
       </c>
       <c r="D232" t="str">
-        <v>质检报告不认可</v>
+        <v>862827072145546</v>
       </c>
       <c r="E232" t="str">
+        <v>手机 7新 小米 小米 MIX FLIP 2 16GB+1T 星云紫 二手优品</v>
+      </c>
+      <c r="F232" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G232" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H232" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I232" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="233">
@@ -4358,13 +7146,25 @@
         <v>郭阳</v>
       </c>
       <c r="C233" t="str">
-        <v>质检</v>
+        <v>1212502475</v>
       </c>
       <c r="D233" t="str">
-        <v>质检报告不认可</v>
+        <v>869717073333253</v>
       </c>
       <c r="E233" t="str">
-        <v>已处理</v>
+        <v>华为 Mate X5</v>
+      </c>
+      <c r="F233" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G233" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H233" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I233" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="234">
@@ -4375,13 +7175,25 @@
         <v>山西-太原-郑连珍</v>
       </c>
       <c r="C234" t="str">
-        <v>质检</v>
+        <v>1212475981</v>
       </c>
       <c r="D234" t="str">
-        <v>质检报告不认可</v>
+        <v>862393062671991</v>
       </c>
       <c r="E234" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 OPPO OPPO Find N3 Flip 12GB+512G 月光缪斯 二手优品</v>
+      </c>
+      <c r="F234" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G234" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H234" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I234" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="235">
@@ -4392,13 +7204,25 @@
         <v>山西-太原-郑连珍</v>
       </c>
       <c r="C235" t="str">
-        <v>质检</v>
+        <v>1212475984</v>
       </c>
       <c r="D235" t="str">
-        <v>质检报告不认可</v>
+        <v>861558069300494</v>
       </c>
       <c r="E235" t="str">
-        <v>已处理</v>
+        <v>手机 7新以下 OPPO OPPO Find N3 Flip 12GB+512G 薄雾玫瑰 二手优品</v>
+      </c>
+      <c r="F235" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G235" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H235" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I235" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="236">
@@ -4409,13 +7233,25 @@
         <v>山西-太原-郑连珍</v>
       </c>
       <c r="C236" t="str">
-        <v>质检</v>
+        <v>1008118719</v>
       </c>
       <c r="D236" t="str">
-        <v>质检报告不认可</v>
+        <v>862393064930775</v>
       </c>
       <c r="E236" t="str">
-        <v>已处理</v>
+        <v>手机 7新 OPPO OPPO Find N3 Flip 12GB+512G 月光缪斯 二手优品</v>
+      </c>
+      <c r="F236" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G236" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H236" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I236" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="237">
@@ -4426,13 +7262,25 @@
         <v>河北-廊坊-于释尧</v>
       </c>
       <c r="C237" t="str">
-        <v>质检</v>
+        <v>1211991563</v>
       </c>
       <c r="D237" t="str">
-        <v>质检报告不认可</v>
+        <v>868040075197373</v>
       </c>
       <c r="E237" t="str">
+        <v>手机 华为 华为 Mate 70 RS 非凡大师 16GB+512G 玄黑 二手优品</v>
+      </c>
+      <c r="F237" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G237" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H237" t="str">
         <v>已评价</v>
+      </c>
+      <c r="I237" t="str">
+        <v>手机</v>
       </c>
     </row>
     <row r="238">
@@ -4443,18 +7291,30 @@
         <v>山西-运城-王涛</v>
       </c>
       <c r="C238" t="str">
-        <v>质检</v>
+        <v>1212426323</v>
       </c>
       <c r="D238" t="str">
-        <v>质检报告不认可</v>
+        <v>865509076240591</v>
       </c>
       <c r="E238" t="str">
-        <v>已处理</v>
+        <v>vivo X Fold 5</v>
+      </c>
+      <c r="F238" t="str">
+        <v>质检</v>
+      </c>
+      <c r="G238" t="str">
+        <v>质检报告不认可</v>
+      </c>
+      <c r="H238" t="str">
+        <v>已处理</v>
+      </c>
+      <c r="I238" t="str">
+        <v>手机</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E238"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I238"/>
   </ignoredErrors>
 </worksheet>
 </file>